--- a/mp_contextuality_outputs/results_workbook.xlsx
+++ b/mp_contextuality_outputs/results_workbook.xlsx
@@ -11,9 +11,9 @@
     <sheet name="queries" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="manifest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="paper_summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="fidelity_by_noise" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="win_rate_by_noise" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="contextuality_by_noise" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="fidelity_by_preservation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="win_rate_by_preservation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="contextuality_by_preservation" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="preserving_advantage" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="mitigation_gain" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="weakest_queries" sheetId="10" state="visible" r:id="rId10"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,7 +433,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>noise_level</t>
+          <t>preservation_level</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="b">
@@ -505,16 +505,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8118165911356373</v>
+        <v>0.7818010388331375</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1878797743055553</v>
+        <v>0.2177327473958325</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8121202256944444</v>
+        <v>0.7822672526041666</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C3" t="b">
@@ -545,16 +545,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7919303998087402</v>
+        <v>0.7532861351752718</v>
       </c>
       <c r="H3" t="n">
-        <v>0.207722981770833</v>
+        <v>0.2463378906249988</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7922770182291666</v>
+        <v>0.753662109375</v>
       </c>
     </row>
     <row r="4">
@@ -565,7 +565,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.891887720891271</v>
+        <v>0.8779337895527767</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1111182857892788</v>
+        <v>0.1233547637426206</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0389434665450603</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8932159407272289</v>
+        <v>0.8794596351289063</v>
       </c>
     </row>
     <row r="5">
@@ -605,7 +605,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -625,16 +625,336 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8799302535400789</v>
+        <v>0.8750965312412814</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1202867296006943</v>
+        <v>0.1252051459418395</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8811238606770833</v>
+        <v>0.876795450846354</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ibm_fez</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8073512542288115</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1923556857638885</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8076443142361112</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ibm_fez</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.755847953802413</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2437337239583323</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7562662760416666</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ibm_fez</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[1, 3, 5]</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8894094511355495</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1111958821614581</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.01322937011718783</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8903588189019097</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ibm_fez</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[1, 3, 5]</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8744894886468915</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1281026204427076</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8757137722439234</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ibm_fez</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.803505612462718</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.196221245659722</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8037787543402778</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ibm_fez</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7796349529110737</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2199978298611105</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7800021701388888</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ibm_fez</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[1, 3, 5]</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8876714058550573</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1142404064414924</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0007107489797988361</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8889678609977554</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ibm_fez</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[1, 3, 5]</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8507250366621675</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1497056749131939</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8519354926215277</v>
       </c>
     </row>
   </sheetData>
@@ -648,13 +968,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>noise_level</t>
+          <t>preservation_level</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -696,7 +1016,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B2" t="b">
@@ -714,19 +1034,19 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.747437</v>
+        <v>0.724731</v>
       </c>
       <c r="G2" t="n">
-        <v>0.747163</v>
+        <v>0.7241919999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.252563</v>
+        <v>0.275269</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B3" t="b">
@@ -744,19 +1064,19 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7530520000000001</v>
+        <v>0.727905</v>
       </c>
       <c r="G3" t="n">
-        <v>0.752741</v>
+        <v>0.727851</v>
       </c>
       <c r="H3" t="n">
-        <v>0.246948</v>
+        <v>0.272095</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B4" t="b">
@@ -774,19 +1094,19 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.773193</v>
+        <v>0.756958</v>
       </c>
       <c r="G4" t="n">
-        <v>0.77295</v>
+        <v>0.756628</v>
       </c>
       <c r="H4" t="n">
-        <v>0.226807</v>
+        <v>0.243042</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B5" t="b">
@@ -804,19 +1124,19 @@
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.811768</v>
+        <v>0.760803</v>
       </c>
       <c r="G5" t="n">
-        <v>0.811154</v>
+        <v>0.7583800000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.188232</v>
+        <v>0.239197</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B6" t="b">
@@ -824,29 +1144,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>R3C2</t>
+          <t>R2C1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.824295</v>
+        <v>0.794144</v>
       </c>
       <c r="G6" t="n">
-        <v>0.822936</v>
+        <v>0.793562</v>
       </c>
       <c r="H6" t="n">
-        <v>0.175705</v>
+        <v>0.205856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B7" t="b">
@@ -864,13 +1184,373 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.84343</v>
+        <v>0.804901</v>
       </c>
       <c r="G7" t="n">
-        <v>0.842253</v>
+        <v>0.803864</v>
       </c>
       <c r="H7" t="n">
-        <v>0.15657</v>
+        <v>0.195099</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.693115</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.692945</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.306885</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.694946</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.694383</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.305054</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.730225</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.730102</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.269775</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.807068</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.806347</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.192932</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.827667</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.82586</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.172333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.834351</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.833032</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.165649</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6972660000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.696944</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.302734</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.720459</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.720112</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.279541</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.724487</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.724167</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.275513</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.79039</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7892130000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.20961</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B18" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.856155</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.855251</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.143845</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B19" t="b">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.857208</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.856341</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.142792</v>
       </c>
     </row>
   </sheetData>
@@ -884,7 +1564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,7 +1575,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>noise_level</t>
+          <t>preservation_level</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -962,7 +1642,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="b">
@@ -983,19 +1663,19 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9197998046875</v>
+        <v>0.907470703125</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9195577570502678</v>
+        <v>0.9071646164568601</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08020019531249982</v>
+        <v>0.09252929687499931</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9197998046875</v>
+        <v>0.907470703125</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0802001953125</v>
+        <v>0.092529296875</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1011,7 +1691,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C3" t="b">
@@ -1032,19 +1712,19 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8011474609375</v>
+        <v>0.7774658203125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8007833053736892</v>
+        <v>0.7771796008239557</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1988525390624998</v>
+        <v>0.2225341796874993</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8011474609375</v>
+        <v>0.7774658203125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1988525390625</v>
+        <v>0.2225341796875</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1060,7 +1740,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -1081,19 +1761,19 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.80810546875</v>
+        <v>0.7833251953125</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8078732200603115</v>
+        <v>0.7822173407794032</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1918945312499998</v>
+        <v>0.2166748046874993</v>
       </c>
       <c r="K4" t="n">
-        <v>0.80810546875</v>
+        <v>0.7833251953125</v>
       </c>
       <c r="L4" t="n">
-        <v>0.19189453125</v>
+        <v>0.2166748046875</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1109,7 +1789,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -1130,19 +1810,19 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8284912109375</v>
+        <v>0.7760009765625</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8281758143580727</v>
+        <v>0.7757696669287653</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1715087890624998</v>
+        <v>0.2239990234374993</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8284912109375</v>
+        <v>0.7760009765625</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1715087890625</v>
+        <v>0.2239990234375</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1158,7 +1838,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -1179,19 +1859,19 @@
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7867431640625</v>
+        <v>0.7420654296875</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7863540058571126</v>
+        <v>0.7412706433817281</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2132568359374998</v>
+        <v>0.2579345703124993</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7867431640625</v>
+        <v>0.7420654296875</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2132568359375</v>
+        <v>0.2579345703125</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1207,7 +1887,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -1228,19 +1908,19 @@
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.795654296875</v>
+        <v>0.7666015625</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7954270768332242</v>
+        <v>0.7662163637273252</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2043457031249998</v>
+        <v>0.2333984374999993</v>
       </c>
       <c r="K7" t="n">
-        <v>0.795654296875</v>
+        <v>0.7666015625</v>
       </c>
       <c r="L7" t="n">
-        <v>0.204345703125</v>
+        <v>0.2333984375</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1256,7 +1936,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="b">
@@ -1277,19 +1957,19 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.810546875</v>
+        <v>0.7762451171875</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8102149840302694</v>
+        <v>0.7757943241147348</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1894531249999998</v>
+        <v>0.2237548828124991</v>
       </c>
       <c r="K8" t="n">
-        <v>0.810546875</v>
+        <v>0.7762451171875</v>
       </c>
       <c r="L8" t="n">
-        <v>0.189453125</v>
+        <v>0.2237548828125</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1305,7 +1985,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="b">
@@ -1326,19 +2006,19 @@
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.773193359375</v>
+        <v>0.730224609375</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7729503929148996</v>
+        <v>0.7301017004856909</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2268066406249998</v>
+        <v>0.2697753906249991</v>
       </c>
       <c r="K9" t="n">
-        <v>0.773193359375</v>
+        <v>0.730224609375</v>
       </c>
       <c r="L9" t="n">
-        <v>0.226806640625</v>
+        <v>0.269775390625</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1354,7 +2034,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="b">
@@ -1375,19 +2055,19 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0.785400390625</v>
+        <v>0.781005859375</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7850127637428894</v>
+        <v>0.7804950927997745</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2145996093749998</v>
+        <v>0.2189941406249991</v>
       </c>
       <c r="K10" t="n">
-        <v>0.785400390625</v>
+        <v>0.781005859375</v>
       </c>
       <c r="L10" t="n">
-        <v>0.214599609375</v>
+        <v>0.218994140625</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1403,7 +2083,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="b">
@@ -1424,19 +2104,19 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.907470703125</v>
+        <v>0.8994140625</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9069932353781001</v>
+        <v>0.8990317200552042</v>
       </c>
       <c r="J11" t="n">
-        <v>0.09252929687499972</v>
+        <v>0.1005859374999988</v>
       </c>
       <c r="K11" t="n">
-        <v>0.907470703125</v>
+        <v>0.8994140625</v>
       </c>
       <c r="L11" t="n">
-        <v>0.092529296875</v>
+        <v>0.1005859375</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1452,7 +2132,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C12" t="b">
@@ -1473,19 +2153,19 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.794677734375</v>
+        <v>0.751220703125</v>
       </c>
       <c r="I12" t="n">
-        <v>0.794496355526437</v>
+        <v>0.7511199279679823</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2053222656249997</v>
+        <v>0.2487792968749988</v>
       </c>
       <c r="K12" t="n">
-        <v>0.794677734375</v>
+        <v>0.751220703125</v>
       </c>
       <c r="L12" t="n">
-        <v>0.205322265625</v>
+        <v>0.248779296875</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1501,7 +2181,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="b">
@@ -1522,19 +2202,19 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.796630859375</v>
+        <v>0.7535400390625</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7962868517590933</v>
+        <v>0.7528991515163165</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2033691406249997</v>
+        <v>0.2464599609374989</v>
       </c>
       <c r="K13" t="n">
-        <v>0.796630859375</v>
+        <v>0.7535400390625</v>
       </c>
       <c r="L13" t="n">
-        <v>0.203369140625</v>
+        <v>0.2464599609375</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1550,7 +2230,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="b">
@@ -1571,19 +2251,19 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7806396484375</v>
+        <v>0.7398681640625</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7801910842678257</v>
+        <v>0.7396539175187117</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2193603515624997</v>
+        <v>0.2601318359374988</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7806396484375</v>
+        <v>0.7398681640625</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2193603515625</v>
+        <v>0.2601318359375</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1599,7 +2279,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="b">
@@ -1620,19 +2300,19 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7474365234375</v>
+        <v>0.6949462890625</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7471631080363668</v>
+        <v>0.6943831889480764</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2525634765624998</v>
+        <v>0.3050537109374988</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7474365234375</v>
+        <v>0.6949462890625</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2525634765625</v>
+        <v>0.3050537109375</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1648,7 +2328,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="b">
@@ -1669,19 +2349,19 @@
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7900390625</v>
+        <v>0.7366943359375</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7896783699029998</v>
+        <v>0.7363167091536665</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2099609374999997</v>
+        <v>0.2633056640624989</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7900390625</v>
+        <v>0.7366943359375</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2099609375</v>
+        <v>0.2633056640625</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1697,7 +2377,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C17" t="b">
@@ -1718,19 +2398,19 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7764892578125</v>
+        <v>0.744873046875</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7760306773123653</v>
+        <v>0.7440801206563383</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2235107421874996</v>
+        <v>0.2551269531249987</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7764892578125</v>
+        <v>0.744873046875</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2235107421875</v>
+        <v>0.255126953125</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1746,7 +2426,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="b">
@@ -1767,19 +2447,19 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7530517578125</v>
+        <v>0.693115234375</v>
       </c>
       <c r="I18" t="n">
-        <v>0.752740972341358</v>
+        <v>0.6929454428455037</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2469482421874996</v>
+        <v>0.3068847656249987</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7530517578125</v>
+        <v>0.693115234375</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2469482421875</v>
+        <v>0.306884765625</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1795,7 +2475,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="b">
@@ -1816,19 +2496,19 @@
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7840576171875</v>
+        <v>0.769287109375</v>
       </c>
       <c r="I19" t="n">
-        <v>0.783792943754117</v>
+        <v>0.7691450379156469</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2159423828124996</v>
+        <v>0.2307128906249987</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7840576171875</v>
+        <v>0.769287109375</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2159423828125</v>
+        <v>0.230712890625</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1844,7 +2524,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C20" t="b">
@@ -1865,23 +2545,23 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9502441257247483</v>
+        <v>0.95147705078125</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9486370986431173</v>
+        <v>0.9495438684388807</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06705065608788521</v>
+        <v>0.06242370605468706</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9502441257247483</v>
+        <v>0.95147705078125</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04975587427525182</v>
+        <v>0.04852294921875004</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.111328125, "0001": 0.115966796875, "0010": 0.0107421875, "0011": 0.012939453125, "0100": 0.1153564453125, "0101": 0.107177734375, "0110": 0.012451171875, "0111": 0.0107421875, "1000": 0.0086669921875, "1001": 0.00830078125, "1010": 0.1180419921875, "1011": 0.1241455078125, "1100": 0.0128173828125, "1101": 0.011474609375, "1110": 0.115478515625, "1111": 0.1043701171875}, "3": {"0000": 0.11474609375, "0001": 0.1087646484375, "0010": 0.016845703125, "0011": 0.01806640625, "0100": 0.1168212890625, "0101": 0.1024169921875, "0110": 0.01611328125, "0111": 0.0157470703125, "1000": 0.01953125, "1001": 0.0185546875, "1010": 0.110107421875, "1011": 0.1019287109375, "1100": 0.017822265625, "1101": 0.018798828125, "1110": 0.1092529296875, "1111": 0.094482421875}, "5": {"0000": 0.116455078125, "0001": 0.108154296875, "0010": 0.0186767578125, "0011": 0.0184326171875, "0100": 0.1141357421875, "0101": 0.1009521484375, "0110": 0.02197265625, "0111": 0.0216064453125, "1000": 0.0216064453125, "1001": 0.021728515625, "1010": 0.1036376953125, "1011": 0.0985107421875, "1100": 0.020263671875, "1101": 0.0191650390625, "1110": 0.10009765625, "1111": 0.0946044921875}}</t>
+          <t>{"1": {"0000": 0.110595703125, "0001": 0.1171875, "0010": 0.0098876953125, "0011": 0.0135498046875, "0100": 0.114990234375, "0101": 0.1055908203125, "0110": 0.0118408203125, "0111": 0.010009765625, "1000": 0.010009765625, "1001": 0.010986328125, "1010": 0.1126708984375, "1011": 0.122314453125, "1100": 0.01171875, "1101": 0.0111083984375, "1110": 0.1104736328125, "1111": 0.1170654296875}, "3": {"0000": 0.1134033203125, "0001": 0.1038818359375, "0010": 0.0191650390625, "0011": 0.01953125, "0100": 0.1085205078125, "0101": 0.109375, "0110": 0.0179443359375, "0111": 0.0185546875, "1000": 0.0184326171875, "1001": 0.019287109375, "1010": 0.1011962890625, "1011": 0.1044921875, "1100": 0.0177001953125, "1101": 0.01806640625, "1110": 0.1024169921875, "1111": 0.1080322265625}, "5": {"0000": 0.1007080078125, "0001": 0.1043701171875, "0010": 0.02294921875, "0011": 0.0205078125, "0100": 0.10302734375, "0101": 0.109619140625, "0110": 0.0247802734375, "0111": 0.020263671875, "1000": 0.021728515625, "1001": 0.0225830078125, "1010": 0.10205078125, "1011": 0.096435546875, "1100": 0.022705078125, "1101": 0.02392578125, "1110": 0.103271484375, "1111": 0.10107421875}}</t>
         </is>
       </c>
     </row>
@@ -1893,7 +2573,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="b">
@@ -1914,23 +2594,23 @@
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9054412841796877</v>
+        <v>0.8783264160156251</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9046795984593538</v>
+        <v>0.8764664168040173</v>
       </c>
       <c r="J21" t="n">
-        <v>0.09515380859374979</v>
+        <v>0.1230926513671871</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9054412841796877</v>
+        <v>0.8783264160156251</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09455871582031268</v>
+        <v>0.1216735839843751</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.0999755859375, "0001": 0.0255126953125, "0010": 0.1015625, "0011": 0.0255126953125, "0100": 0.1011962890625, "0101": 0.025634765625, "0110": 0.105224609375, "0111": 0.0245361328125, "1000": 0.027099609375, "1001": 0.1019287109375, "1010": 0.0225830078125, "1011": 0.095703125, "1100": 0.0216064453125, "1101": 0.103759765625, "1110": 0.0242919921875, "1111": 0.0938720703125}, "3": {"0000": 0.0877685546875, "0001": 0.0450439453125, "0010": 0.0855712890625, "0011": 0.0419921875, "0100": 0.0892333984375, "0101": 0.044189453125, "0110": 0.0899658203125, "0111": 0.0401611328125, "1000": 0.044189453125, "1001": 0.0767822265625, "1010": 0.042724609375, "1011": 0.076416015625, "1100": 0.0418701171875, "1101": 0.077392578125, "1110": 0.0394287109375, "1111": 0.0772705078125}, "5": {"0000": 0.08056640625, "0001": 0.052490234375, "0010": 0.0748291015625, "0011": 0.049560546875, "0100": 0.0782470703125, "0101": 0.051513671875, "0110": 0.0716552734375, "0111": 0.046875, "1000": 0.047607421875, "1001": 0.0721435546875, "1010": 0.0509033203125, "1011": 0.07763671875, "1100": 0.0523681640625, "1101": 0.0740966796875, "1110": 0.0489501953125, "1111": 0.070556640625}}</t>
+          <t>{"1": {"0000": 0.10400390625, "0001": 0.028076171875, "0010": 0.0916748046875, "0011": 0.03271484375, "0100": 0.09375, "0101": 0.0267333984375, "0110": 0.0972900390625, "0111": 0.0257568359375, "1000": 0.0291748046875, "1001": 0.0933837890625, "1010": 0.0262451171875, "1011": 0.10546875, "1100": 0.0250244140625, "1101": 0.0980224609375, "1110": 0.027099609375, "1111": 0.0955810546875}, "3": {"0000": 0.08203125, "0001": 0.044189453125, "0010": 0.0819091796875, "0011": 0.042724609375, "0100": 0.0855712890625, "0101": 0.0452880859375, "0110": 0.0802001953125, "0111": 0.049560546875, "1000": 0.0440673828125, "1001": 0.078369140625, "1010": 0.0458984375, "1011": 0.0792236328125, "1100": 0.0452880859375, "1101": 0.082763671875, "1110": 0.040771484375, "1111": 0.0721435546875}, "5": {"0000": 0.078369140625, "0001": 0.05615234375, "0010": 0.071044921875, "0011": 0.0477294921875, "0100": 0.076904296875, "0101": 0.054931640625, "0110": 0.0738525390625, "0111": 0.05029296875, "1000": 0.0511474609375, "1001": 0.071044921875, "1010": 0.0489501953125, "1011": 0.0738525390625, "1100": 0.052490234375, "1101": 0.072998046875, "1110": 0.05126953125, "1111": 0.0689697265625}}</t>
         </is>
       </c>
     </row>
@@ -1942,7 +2622,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C22" t="b">
@@ -1963,23 +2643,23 @@
         <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>0.898468017578125</v>
+        <v>0.8912048339843748</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8968378213708306</v>
+        <v>0.8883744768097013</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1026611328124998</v>
+        <v>0.1144561767578121</v>
       </c>
       <c r="K22" t="n">
-        <v>0.898468017578125</v>
+        <v>0.8912048339843748</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1015319824218751</v>
+        <v>0.1087951660156252</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.02197265625, "0001": 0.095458984375, "0010": 0.09814453125, "0011": 0.0205078125, "0100": 0.0267333984375, "0101": 0.1033935546875, "0110": 0.1060791015625, "0111": 0.023193359375, "1000": 0.0972900390625, "1001": 0.02587890625, "1010": 0.0235595703125, "1011": 0.0989990234375, "1100": 0.106201171875, "1101": 0.0250244140625, "1110": 0.0205078125, "1111": 0.1070556640625}, "3": {"0000": 0.044189453125, "0001": 0.08740234375, "0010": 0.085693359375, "0011": 0.0411376953125, "0100": 0.042724609375, "0101": 0.088623046875, "0110": 0.085205078125, "0111": 0.0330810546875, "1000": 0.090087890625, "1001": 0.0406494140625, "1010": 0.0406494140625, "1011": 0.076904296875, "1100": 0.0859375, "1101": 0.0338134765625, "1110": 0.04345703125, "1111": 0.0804443359375}, "5": {"0000": 0.052734375, "0001": 0.080322265625, "0010": 0.080322265625, "0011": 0.049072265625, "0100": 0.0543212890625, "0101": 0.07763671875, "0110": 0.07666015625, "0111": 0.05029296875, "1000": 0.0751953125, "1001": 0.051513671875, "1010": 0.04736328125, "1011": 0.064453125, "1100": 0.07666015625, "1101": 0.046630859375, "1110": 0.047607421875, "1111": 0.0692138671875}}</t>
+          <t>{"1": {"0000": 0.0206298828125, "0001": 0.0982666015625, "0010": 0.1070556640625, "0011": 0.0279541015625, "0100": 0.0252685546875, "0101": 0.099365234375, "0110": 0.091552734375, "0111": 0.0291748046875, "1000": 0.10205078125, "1001": 0.029052734375, "1010": 0.027587890625, "1011": 0.0977783203125, "1100": 0.089111328125, "1101": 0.02294921875, "1110": 0.02880859375, "1111": 0.1033935546875}, "3": {"0000": 0.046875, "0001": 0.0819091796875, "0010": 0.08447265625, "0011": 0.0472412109375, "0100": 0.049560546875, "0101": 0.0867919921875, "0110": 0.0836181640625, "0111": 0.0426025390625, "1000": 0.083984375, "1001": 0.0443115234375, "1010": 0.040771484375, "1011": 0.0728759765625, "1100": 0.0797119140625, "1101": 0.03759765625, "1110": 0.0452880859375, "1111": 0.0723876953125}, "5": {"0000": 0.0543212890625, "0001": 0.0697021484375, "0010": 0.0772705078125, "0011": 0.0540771484375, "0100": 0.0574951171875, "0101": 0.0791015625, "0110": 0.068603515625, "0111": 0.0452880859375, "1000": 0.0804443359375, "1001": 0.0531005859375, "1010": 0.04931640625, "1011": 0.0660400390625, "1100": 0.072265625, "1101": 0.0498046875, "1110": 0.0504150390625, "1111": 0.07275390625}}</t>
         </is>
       </c>
     </row>
@@ -1991,7 +2671,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C23" t="b">
@@ -2012,23 +2692,23 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9238891601562498</v>
+        <v>0.9061950657695337</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9215927069529658</v>
+        <v>0.9056505148138158</v>
       </c>
       <c r="J23" t="n">
-        <v>0.08963012695312506</v>
+        <v>0.0938049342304656</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9238891601562498</v>
+        <v>0.9061950657695337</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07611083984375022</v>
+        <v>0.09380493423046632</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.1053466796875, "0001": 0.1043701171875, "0010": 0.0240478515625, "0011": 0.02001953125, "0100": 0.02099609375, "0101": 0.02392578125, "0110": 0.0987548828125, "0111": 0.1109619140625, "1000": 0.102294921875, "1001": 0.0966796875, "1010": 0.01953125, "1011": 0.025634765625, "1100": 0.0242919921875, "1101": 0.0223388671875, "1110": 0.0992431640625, "1111": 0.1015625}, "3": {"0000": 0.0830078125, "0001": 0.0858154296875, "0010": 0.043701171875, "0011": 0.0406494140625, "0100": 0.042724609375, "0101": 0.0406494140625, "0110": 0.0911865234375, "0111": 0.07763671875, "1000": 0.092041015625, "1001": 0.0806884765625, "1010": 0.041259765625, "1011": 0.0391845703125, "1100": 0.0443115234375, "1101": 0.0401611328125, "1110": 0.079345703125, "1111": 0.07763671875}, "5": {"0000": 0.0787353515625, "0001": 0.0755615234375, "0010": 0.05126953125, "0011": 0.049560546875, "0100": 0.05615234375, "0101": 0.049072265625, "0110": 0.0760498046875, "0111": 0.0733642578125, "1000": 0.0721435546875, "1001": 0.06884765625, "1010": 0.0504150390625, "1011": 0.049560546875, "1100": 0.0504150390625, "1101": 0.0513916015625, "1110": 0.07763671875, "1111": 0.06982421875}}</t>
+          <t>{"1": {"0000": 0.0965576171875, "0001": 0.0985107421875, "0010": 0.0208740234375, "0011": 0.026611328125, "0100": 0.0330810546875, "0101": 0.02587890625, "0110": 0.1014404296875, "0111": 0.102294921875, "1000": 0.0975341796875, "1001": 0.0938720703125, "1010": 0.029541015625, "1011": 0.0262451171875, "1100": 0.0277099609375, "1101": 0.02734375, "1110": 0.0966796875, "1111": 0.0958251953125}, "3": {"0000": 0.0850830078125, "0001": 0.07666015625, "0010": 0.051513671875, "0011": 0.0457763671875, "0100": 0.048095703125, "0101": 0.04833984375, "0110": 0.07666015625, "0111": 0.07861328125, "1000": 0.0792236328125, "1001": 0.0721435546875, "1010": 0.04638671875, "1011": 0.0457763671875, "1100": 0.0462646484375, "1101": 0.0484619140625, "1110": 0.0726318359375, "1111": 0.078369140625}, "5": {"0000": 0.0791015625, "0001": 0.072021484375, "0010": 0.0489501953125, "0011": 0.05322265625, "0100": 0.0543212890625, "0101": 0.053955078125, "0110": 0.070556640625, "0111": 0.0733642578125, "1000": 0.0736083984375, "1001": 0.071533203125, "1010": 0.0513916015625, "1011": 0.04931640625, "1100": 0.05322265625, "1101": 0.0513916015625, "1110": 0.072998046875, "1111": 0.071044921875}}</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2720,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="b">
@@ -2061,23 +2741,23 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8724822998046875</v>
+        <v>0.8343505859374999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8700913699750145</v>
+        <v>0.8330318349796411</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1339874267578124</v>
+        <v>0.1656494140624994</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8724822998046875</v>
+        <v>0.8343505859374999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1275177001953126</v>
+        <v>0.1656494140625002</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.1036376953125, "0001": 0.0244140625, "0010": 0.105224609375, "0011": 0.0281982421875, "0100": 0.027587890625, "0101": 0.095458984375, "0110": 0.0250244140625, "0111": 0.0938720703125, "1000": 0.0941162109375, "1001": 0.025146484375, "1010": 0.0966796875, "1011": 0.024169921875, "1100": 0.03125, "1101": 0.103271484375, "1110": 0.0274658203125, "1111": 0.094482421875}, "3": {"0000": 0.096435546875, "0001": 0.041259765625, "0010": 0.0792236328125, "0011": 0.0450439453125, "0100": 0.04638671875, "0101": 0.086669921875, "0110": 0.044189453125, "0111": 0.0823974609375, "1000": 0.085693359375, "1001": 0.041015625, "1010": 0.0787353515625, "1011": 0.0374755859375, "1100": 0.0455322265625, "1101": 0.072509765625, "1110": 0.0379638671875, "1111": 0.0794677734375}, "5": {"0000": 0.07958984375, "0001": 0.0521240234375, "0010": 0.0745849609375, "0011": 0.0484619140625, "0100": 0.05224609375, "0101": 0.0816650390625, "0110": 0.0482177734375, "0111": 0.0728759765625, "1000": 0.0718994140625, "1001": 0.0479736328125, "1010": 0.0704345703125, "1011": 0.04931640625, "1100": 0.052001953125, "1101": 0.0726318359375, "1110": 0.052978515625, "1111": 0.072998046875}}</t>
+          <t>{"1": {"0000": 0.09619140625, "0001": 0.0343017578125, "0010": 0.0936279296875, "0011": 0.0341796875, "0100": 0.033447265625, "0101": 0.088623046875, "0110": 0.0318603515625, "0111": 0.09228515625, "1000": 0.0919189453125, "1001": 0.0316162109375, "1010": 0.09765625, "1011": 0.029296875, "1100": 0.0318603515625, "1101": 0.100830078125, "1110": 0.026123046875, "1111": 0.086181640625}, "3": {"0000": 0.0828857421875, "0001": 0.046875, "0010": 0.0772705078125, "0011": 0.048095703125, "0100": 0.05712890625, "0101": 0.080078125, "0110": 0.0447998046875, "0111": 0.0811767578125, "1000": 0.079833984375, "1001": 0.044921875, "1010": 0.0794677734375, "1011": 0.0439453125, "1100": 0.0450439453125, "1101": 0.073486328125, "1110": 0.044677734375, "1111": 0.0703125}, "5": {"0000": 0.0748291015625, "0001": 0.05419921875, "0010": 0.0751953125, "0011": 0.0546875, "0100": 0.052490234375, "0101": 0.072021484375, "0110": 0.056884765625, "0111": 0.07177734375, "1000": 0.0709228515625, "1001": 0.0509033203125, "1010": 0.064208984375, "1011": 0.05029296875, "1100": 0.0584716796875, "1101": 0.06884765625, "1110": 0.052001953125, "1111": 0.072265625}}</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2769,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C25" t="b">
@@ -2110,23 +2790,23 @@
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>0.92205810546875</v>
+        <v>0.8879241943359374</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9215303043039238</v>
+        <v>0.8860851222018129</v>
       </c>
       <c r="J25" t="n">
-        <v>0.07794189453124994</v>
+        <v>0.1162567138671869</v>
       </c>
       <c r="K25" t="n">
-        <v>0.92205810546875</v>
+        <v>0.8879241943359374</v>
       </c>
       <c r="L25" t="n">
-        <v>0.07794189453125021</v>
+        <v>0.1120758056640626</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.025390625, "0001": 0.099853515625, "0010": 0.0999755859375, "0011": 0.024169921875, "0100": 0.0986328125, "0101": 0.025146484375, "0110": 0.024658203125, "0111": 0.101806640625, "1000": 0.0247802734375, "1001": 0.101806640625, "1010": 0.0992431640625, "1011": 0.024169921875, "1100": 0.101318359375, "1101": 0.0247802734375, "1110": 0.024658203125, "1111": 0.099609375}, "3": {"0000": 0.047607421875, "0001": 0.0814208984375, "0010": 0.087646484375, "0011": 0.042724609375, "0100": 0.085693359375, "0101": 0.0443115234375, "0110": 0.0438232421875, "0111": 0.08349609375, "1000": 0.0474853515625, "1001": 0.0762939453125, "1010": 0.078369140625, "1011": 0.040283203125, "1100": 0.0797119140625, "1101": 0.0430908203125, "1110": 0.0419921875, "1111": 0.0760498046875}, "5": {"0000": 0.056884765625, "0001": 0.0767822265625, "0010": 0.07421875, "0011": 0.048095703125, "0100": 0.082275390625, "0101": 0.051025390625, "0110": 0.0465087890625, "0111": 0.0743408203125, "1000": 0.047119140625, "1001": 0.0738525390625, "1010": 0.0751953125, "1011": 0.045166015625, "1100": 0.07958984375, "1101": 0.0445556640625, "1110": 0.05078125, "1111": 0.0736083984375}}</t>
+          <t>{"1": {"0000": 0.02880859375, "0001": 0.0931396484375, "0010": 0.1038818359375, "0011": 0.0244140625, "0100": 0.1005859375, "0101": 0.027099609375, "0110": 0.0294189453125, "0111": 0.09912109375, "1000": 0.0283203125, "1001": 0.0950927734375, "1010": 0.093505859375, "1011": 0.0252685546875, "1100": 0.096435546875, "1101": 0.02734375, "1110": 0.0262451171875, "1111": 0.101318359375}, "3": {"0000": 0.049072265625, "0001": 0.0843505859375, "0010": 0.0916748046875, "0011": 0.0482177734375, "0100": 0.0850830078125, "0101": 0.046875, "0110": 0.048828125, "0111": 0.075927734375, "1000": 0.0462646484375, "1001": 0.0712890625, "1010": 0.080078125, "1011": 0.0433349609375, "1100": 0.078857421875, "1101": 0.0362548828125, "1110": 0.043212890625, "1111": 0.0706787109375}, "5": {"0000": 0.0509033203125, "0001": 0.0689697265625, "0010": 0.0758056640625, "0011": 0.0552978515625, "0100": 0.0733642578125, "0101": 0.0538330078125, "0110": 0.0546875, "0111": 0.0791015625, "1000": 0.0540771484375, "1001": 0.0701904296875, "1010": 0.0673828125, "1011": 0.0517578125, "1100": 0.070556640625, "1101": 0.04736328125, "1110": 0.05322265625, "1111": 0.073486328125}}</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2818,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C26" t="b">
@@ -2159,23 +2839,23 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.888671875</v>
+        <v>0.9030609130859373</v>
       </c>
       <c r="I26" t="n">
-        <v>0.888625742063774</v>
+        <v>0.9011557769348011</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1113281249999999</v>
+        <v>0.09710693359374947</v>
       </c>
       <c r="K26" t="n">
-        <v>0.888671875</v>
+        <v>0.9030609130859373</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1113281250000001</v>
+        <v>0.09693908691406262</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.1041259765625, "0001": 0.1014404296875, "0010": 0.025390625, "0011": 0.020263671875, "0100": 0.0257568359375, "0101": 0.0269775390625, "0110": 0.1007080078125, "0111": 0.09619140625, "1000": 0.025390625, "1001": 0.02490234375, "1010": 0.101806640625, "1011": 0.1004638671875, "1100": 0.1029052734375, "1101": 0.099365234375, "1110": 0.0220947265625, "1111": 0.022216796875}, "3": {"0000": 0.0927734375, "0001": 0.086181640625, "0010": 0.042724609375, "0011": 0.040771484375, "0100": 0.040283203125, "0101": 0.040771484375, "0110": 0.084716796875, "0111": 0.0787353515625, "1000": 0.0411376953125, "1001": 0.0396728515625, "1010": 0.085205078125, "1011": 0.083984375, "1100": 0.088134765625, "1101": 0.0816650390625, "1110": 0.03662109375, "1111": 0.03662109375}, "5": {"0000": 0.0758056640625, "0001": 0.0777587890625, "0010": 0.0523681640625, "0011": 0.0460205078125, "0100": 0.05224609375, "0101": 0.0501708984375, "0110": 0.0762939453125, "0111": 0.0772705078125, "1000": 0.054443359375, "1001": 0.0450439453125, "1010": 0.0753173828125, "1011": 0.0697021484375, "1100": 0.079833984375, "1101": 0.0740966796875, "1110": 0.046875, "1111": 0.0467529296875}}</t>
+          <t>{"1": {"0000": 0.0928955078125, "0001": 0.1038818359375, "0010": 0.023681640625, "0011": 0.0240478515625, "0100": 0.0289306640625, "0101": 0.0233154296875, "0110": 0.09765625, "0111": 0.1051025390625, "1000": 0.02392578125, "1001": 0.0257568359375, "1010": 0.1024169921875, "1011": 0.103271484375, "1100": 0.1058349609375, "1101": 0.0965576171875, "1110": 0.021484375, "1111": 0.021240234375}, "3": {"0000": 0.087646484375, "0001": 0.0836181640625, "0010": 0.0428466796875, "0011": 0.041748046875, "0100": 0.042236328125, "0101": 0.0457763671875, "0110": 0.088623046875, "0111": 0.0789794921875, "1000": 0.0445556640625, "1001": 0.039794921875, "1010": 0.0792236328125, "1011": 0.0814208984375, "1100": 0.0872802734375, "1101": 0.0791015625, "1110": 0.0382080078125, "1111": 0.0389404296875}, "5": {"0000": 0.0728759765625, "0001": 0.071044921875, "0010": 0.05126953125, "0011": 0.0518798828125, "0100": 0.0513916015625, "0101": 0.0535888671875, "0110": 0.0804443359375, "0111": 0.071533203125, "1000": 0.0523681640625, "1001": 0.047119140625, "1010": 0.0703125, "1011": 0.070068359375, "1100": 0.0777587890625, "1101": 0.07568359375, "1110": 0.051025390625, "1111": 0.0516357421875}}</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2867,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C27" t="b">
@@ -2208,23 +2888,23 @@
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8242950439453125</v>
+        <v>0.80706787109375</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8229357878890723</v>
+        <v>0.8063467549377259</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1757049560546874</v>
+        <v>0.1929321289062491</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8242950439453125</v>
+        <v>0.80706787109375</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1757049560546876</v>
+        <v>0.19293212890625</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.0987548828125, "0001": 0.0260009765625, "0010": 0.09033203125, "0011": 0.0322265625, "0100": 0.032470703125, "0101": 0.0985107421875, "0110": 0.0330810546875, "0111": 0.0916748046875, "1000": 0.0281982421875, "1001": 0.098388671875, "1010": 0.0301513671875, "1011": 0.0931396484375, "1100": 0.0931396484375, "1101": 0.03173828125, "1110": 0.088134765625, "1111": 0.0340576171875}, "3": {"0000": 0.0838623046875, "0001": 0.0504150390625, "0010": 0.0811767578125, "0011": 0.0457763671875, "0100": 0.0509033203125, "0101": 0.079833984375, "0110": 0.0423583984375, "0111": 0.076904296875, "1000": 0.0440673828125, "1001": 0.07861328125, "1010": 0.04248046875, "1011": 0.077880859375, "1100": 0.08544921875, "1101": 0.0400390625, "1110": 0.0811767578125, "1111": 0.0390625}, "5": {"0000": 0.0797119140625, "0001": 0.05029296875, "0010": 0.0711669921875, "0011": 0.0521240234375, "0100": 0.0567626953125, "0101": 0.074951171875, "0110": 0.0531005859375, "0111": 0.074462890625, "1000": 0.0535888671875, "1001": 0.073486328125, "1010": 0.0538330078125, "1011": 0.0689697265625, "1100": 0.0738525390625, "1101": 0.0457763671875, "1110": 0.07080078125, "1111": 0.047119140625}}</t>
+          <t>{"1": {"0000": 0.099609375, "0001": 0.03759765625, "0010": 0.0924072265625, "0011": 0.0322265625, "0100": 0.0341796875, "0101": 0.0904541015625, "0110": 0.03173828125, "0111": 0.092529296875, "1000": 0.031982421875, "1001": 0.0924072265625, "1010": 0.0316162109375, "1011": 0.0916748046875, "1100": 0.091796875, "1101": 0.0328369140625, "1110": 0.0869140625, "1111": 0.030029296875}, "3": {"0000": 0.0875244140625, "0001": 0.0469970703125, "0010": 0.077880859375, "0011": 0.0469970703125, "0100": 0.05029296875, "0101": 0.0806884765625, "0110": 0.0472412109375, "0111": 0.068603515625, "1000": 0.0517578125, "1001": 0.0782470703125, "1010": 0.0501708984375, "1011": 0.0709228515625, "1100": 0.08203125, "1101": 0.044677734375, "1110": 0.07568359375, "1111": 0.040283203125}, "5": {"0000": 0.0697021484375, "0001": 0.0599365234375, "0010": 0.0643310546875, "0011": 0.06103515625, "0100": 0.056884765625, "0101": 0.0665283203125, "0110": 0.05810546875, "0111": 0.066650390625, "1000": 0.0576171875, "1001": 0.0673828125, "1010": 0.05810546875, "1011": 0.0611572265625, "1100": 0.070068359375, "1101": 0.05810546875, "1110": 0.0693359375, "1111": 0.0550537109375}}</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2916,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="b">
@@ -2257,23 +2937,23 @@
         <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8533935546875</v>
+        <v>0.85552978515625</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8520590583633867</v>
+        <v>0.8547493400545941</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1466064453124999</v>
+        <v>0.1444702148437491</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8533935546875</v>
+        <v>0.85552978515625</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1466064453125001</v>
+        <v>0.14447021484375</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.029296875, "0001": 0.0968017578125, "0010": 0.101318359375, "0011": 0.0255126953125, "0100": 0.09716796875, "0101": 0.0277099609375, "0110": 0.029052734375, "0111": 0.095458984375, "1000": 0.1009521484375, "1001": 0.0260009765625, "1010": 0.025390625, "1011": 0.0958251953125, "1100": 0.028076171875, "1101": 0.0953369140625, "1110": 0.102294921875, "1111": 0.0238037109375}, "3": {"0000": 0.0430908203125, "0001": 0.0853271484375, "0010": 0.0926513671875, "0011": 0.042236328125, "0100": 0.09033203125, "0101": 0.0435791015625, "0110": 0.0400390625, "0111": 0.083740234375, "1000": 0.081787109375, "1001": 0.03515625, "1010": 0.040283203125, "1011": 0.08544921875, "1100": 0.041259765625, "1101": 0.0836181640625, "1110": 0.0772705078125, "1111": 0.0341796875}, "5": {"0000": 0.0521240234375, "0001": 0.0771484375, "0010": 0.070556640625, "0011": 0.0482177734375, "0100": 0.0826416015625, "0101": 0.048095703125, "0110": 0.0501708984375, "0111": 0.0758056640625, "1000": 0.0810546875, "1001": 0.0472412109375, "1010": 0.043701171875, "1011": 0.07421875, "1100": 0.0517578125, "1101": 0.0767822265625, "1110": 0.0789794921875, "1111": 0.04150390625}}</t>
+          <t>{"1": {"0000": 0.02880859375, "0001": 0.104736328125, "0010": 0.1025390625, "0011": 0.02685546875, "0100": 0.0986328125, "0101": 0.031494140625, "0110": 0.0264892578125, "0111": 0.0936279296875, "1000": 0.093994140625, "1001": 0.024169921875, "1010": 0.0235595703125, "1011": 0.1043701171875, "1100": 0.0289306640625, "1101": 0.0927734375, "1110": 0.0941162109375, "1111": 0.02490234375}, "3": {"0000": 0.0419921875, "0001": 0.095703125, "0010": 0.0865478515625, "0011": 0.0384521484375, "0100": 0.08984375, "0101": 0.0386962890625, "0110": 0.0435791015625, "0111": 0.08056640625, "1000": 0.0831298828125, "1001": 0.0406494140625, "1010": 0.039306640625, "1011": 0.08056640625, "1100": 0.0416259765625, "1101": 0.076171875, "1110": 0.083740234375, "1111": 0.0394287109375}, "5": {"0000": 0.0517578125, "0001": 0.0811767578125, "0010": 0.0765380859375, "0011": 0.045654296875, "0100": 0.080322265625, "0101": 0.054443359375, "0110": 0.0484619140625, "0111": 0.075439453125, "1000": 0.076171875, "1001": 0.0467529296875, "1010": 0.0465087890625, "1011": 0.0703125, "1100": 0.0491943359375, "1101": 0.0736083984375, "1110": 0.078125, "1111": 0.0455322265625}}</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2965,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C29" t="b">
@@ -2306,23 +2986,23 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.947906494140625</v>
+        <v>0.92791748046875</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9470429189859522</v>
+        <v>0.9270687359285498</v>
       </c>
       <c r="J29" t="n">
-        <v>0.05862426757812495</v>
+        <v>0.07284545898437417</v>
       </c>
       <c r="K29" t="n">
-        <v>0.947906494140625</v>
+        <v>0.92791748046875</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05209350585937505</v>
+        <v>0.07208251953124999</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.1163330078125, "0001": 0.1107177734375, "0010": 0.0106201171875, "0011": 0.0101318359375, "0100": 0.1146240234375, "0101": 0.1080322265625, "0110": 0.0123291015625, "0111": 0.01025390625, "1000": 0.010986328125, "1001": 0.010009765625, "1010": 0.1199951171875, "1011": 0.115234375, "1100": 0.01123046875, "1101": 0.0115966796875, "1110": 0.114990234375, "1111": 0.1129150390625}, "3": {"0000": 0.1138916015625, "0001": 0.1138916015625, "0010": 0.0164794921875, "0011": 0.018310546875, "0100": 0.113037109375, "0101": 0.1031494140625, "0110": 0.0186767578125, "0111": 0.018798828125, "1000": 0.018310546875, "1001": 0.0198974609375, "1010": 0.107421875, "1011": 0.104248046875, "1100": 0.015869140625, "1101": 0.0150146484375, "1110": 0.107177734375, "1111": 0.0958251953125}, "5": {"0000": 0.111572265625, "0001": 0.1129150390625, "0010": 0.02294921875, "0011": 0.01953125, "0100": 0.105224609375, "0101": 0.10107421875, "0110": 0.0233154296875, "0111": 0.0201416015625, "1000": 0.0233154296875, "1001": 0.021728515625, "1010": 0.1002197265625, "1011": 0.099365234375, "1100": 0.0208740234375, "1101": 0.0224609375, "1110": 0.0985107421875, "1111": 0.0968017578125}}</t>
+          <t>{"1": {"0000": 0.1107177734375, "0001": 0.1053466796875, "0010": 0.01318359375, "0011": 0.0130615234375, "0100": 0.1123046875, "0101": 0.10986328125, "0110": 0.0155029296875, "0111": 0.0135498046875, "1000": 0.01171875, "1001": 0.015380859375, "1010": 0.1124267578125, "1011": 0.11083984375, "1100": 0.012939453125, "1101": 0.011962890625, "1110": 0.1134033203125, "1111": 0.1177978515625}, "3": {"0000": 0.103271484375, "0001": 0.1048583984375, "0010": 0.0177001953125, "0011": 0.0201416015625, "0100": 0.105224609375, "0101": 0.1068115234375, "0110": 0.02099609375, "0111": 0.0225830078125, "1000": 0.023193359375, "1001": 0.0218505859375, "1010": 0.0980224609375, "1011": 0.1055908203125, "1100": 0.0218505859375, "1101": 0.0191650390625, "1110": 0.102294921875, "1111": 0.1064453125}, "5": {"0000": 0.098876953125, "0001": 0.0975341796875, "0010": 0.026123046875, "0011": 0.02880859375, "0100": 0.1060791015625, "0101": 0.098876953125, "0110": 0.027587890625, "0111": 0.02734375, "1000": 0.025634765625, "1001": 0.026123046875, "1010": 0.0926513671875, "1011": 0.0977783203125, "1100": 0.024658203125, "1101": 0.0277099609375, "1110": 0.093017578125, "1111": 0.1011962890625}}</t>
         </is>
       </c>
     </row>
@@ -2334,7 +3014,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C30" t="b">
@@ -2355,23 +3035,23 @@
         <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8751373291015625</v>
+        <v>0.8503723144531249</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8734259123725996</v>
+        <v>0.8493253380906117</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1248626708984373</v>
+        <v>0.149627685546874</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8751373291015625</v>
+        <v>0.8503723144531249</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1248626708984377</v>
+        <v>0.1496276855468752</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.0965576171875, "0001": 0.0284423828125, "0010": 0.0948486328125, "0011": 0.028076171875, "0100": 0.107421875, "0101": 0.0269775390625, "0110": 0.103515625, "0111": 0.0262451171875, "1000": 0.02392578125, "1001": 0.0946044921875, "1010": 0.0299072265625, "1011": 0.099853515625, "1100": 0.0257568359375, "1101": 0.09228515625, "1110": 0.0255126953125, "1111": 0.0960693359375}, "3": {"0000": 0.0924072265625, "0001": 0.0390625, "0010": 0.0830078125, "0011": 0.0406494140625, "0100": 0.086669921875, "0101": 0.042236328125, "0110": 0.08349609375, "0111": 0.0433349609375, "1000": 0.0435791015625, "1001": 0.0751953125, "1010": 0.04541015625, "1011": 0.073974609375, "1100": 0.0460205078125, "1101": 0.080078125, "1110": 0.043701171875, "1111": 0.0811767578125}, "5": {"0000": 0.08447265625, "0001": 0.0531005859375, "0010": 0.0726318359375, "0011": 0.0474853515625, "0100": 0.0838623046875, "0101": 0.0494384765625, "0110": 0.072021484375, "0111": 0.04931640625, "1000": 0.053955078125, "1001": 0.072509765625, "1010": 0.0484619140625, "1011": 0.070068359375, "1100": 0.056884765625, "1101": 0.0714111328125, "1110": 0.0467529296875, "1111": 0.067626953125}}</t>
+          <t>{"1": {"0000": 0.097900390625, "0001": 0.0374755859375, "0010": 0.092529296875, "0011": 0.03125, "0100": 0.095947265625, "0101": 0.0306396484375, "0110": 0.092529296875, "0111": 0.0311279296875, "1000": 0.0306396484375, "1001": 0.087646484375, "1010": 0.0301513671875, "1011": 0.092529296875, "1100": 0.0286865234375, "1101": 0.0927734375, "1110": 0.033203125, "1111": 0.094970703125}, "3": {"0000": 0.0845947265625, "0001": 0.050048828125, "0010": 0.0804443359375, "0011": 0.0491943359375, "0100": 0.080322265625, "0101": 0.05029296875, "0110": 0.0665283203125, "0111": 0.0491943359375, "1000": 0.050048828125, "1001": 0.073974609375, "1010": 0.0478515625, "1011": 0.07080078125, "1100": 0.0516357421875, "1101": 0.078857421875, "1110": 0.046630859375, "1111": 0.069580078125}, "5": {"0000": 0.0780029296875, "0001": 0.058837890625, "0010": 0.0625, "0011": 0.0576171875, "0100": 0.0714111328125, "0101": 0.060302734375, "0110": 0.0714111328125, "0111": 0.0560302734375, "1000": 0.0565185546875, "1001": 0.0660400390625, "1010": 0.0501708984375, "1011": 0.0625, "1100": 0.0574951171875, "1101": 0.070068359375, "1110": 0.052490234375, "1111": 0.068603515625}}</t>
         </is>
       </c>
     </row>
@@ -2383,7 +3063,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C31" t="b">
@@ -2404,23 +3084,23 @@
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>0.88623046875</v>
+        <v>0.8887176513671873</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8842939252138967</v>
+        <v>0.8850578496535444</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1137695312499998</v>
+        <v>0.1142120361328118</v>
       </c>
       <c r="K31" t="n">
-        <v>0.88623046875</v>
+        <v>0.8887176513671873</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1137695312500001</v>
+        <v>0.1112823486328127</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.02880859375, "0001": 0.0928955078125, "0010": 0.104248046875, "0011": 0.0264892578125, "0100": 0.028076171875, "0101": 0.10009765625, "0110": 0.0948486328125, "0111": 0.024169921875, "1000": 0.094970703125, "1001": 0.0260009765625, "1010": 0.02490234375, "1011": 0.101806640625, "1100": 0.104248046875, "1101": 0.0224609375, "1110": 0.0238037109375, "1111": 0.1021728515625}, "3": {"0000": 0.04833984375, "0001": 0.0869140625, "0010": 0.089599609375, "0011": 0.0439453125, "0100": 0.0462646484375, "0101": 0.0821533203125, "0110": 0.08056640625, "0111": 0.038330078125, "1000": 0.0872802734375, "1001": 0.0421142578125, "1010": 0.0396728515625, "1011": 0.07421875, "1100": 0.07958984375, "1101": 0.03955078125, "1110": 0.0418701171875, "1111": 0.07958984375}, "5": {"0000": 0.0535888671875, "0001": 0.078369140625, "0010": 0.07470703125, "0011": 0.0537109375, "0100": 0.0540771484375, "0101": 0.0745849609375, "0110": 0.0748291015625, "0111": 0.0482177734375, "1000": 0.0755615234375, "1001": 0.0565185546875, "1010": 0.0479736328125, "1011": 0.06787109375, "1100": 0.0750732421875, "1101": 0.0506591796875, "1110": 0.0487060546875, "1111": 0.0655517578125}}</t>
+          <t>{"1": {"0000": 0.0277099609375, "0001": 0.0858154296875, "0010": 0.100830078125, "0011": 0.0311279296875, "0100": 0.02978515625, "0101": 0.1060791015625, "0110": 0.089111328125, "0111": 0.0281982421875, "1000": 0.1024169921875, "1001": 0.03173828125, "1010": 0.030029296875, "1011": 0.0933837890625, "1100": 0.0859375, "1101": 0.0244140625, "1110": 0.0303955078125, "1111": 0.10302734375}, "3": {"0000": 0.048095703125, "0001": 0.08203125, "0010": 0.0810546875, "0011": 0.052978515625, "0100": 0.0516357421875, "0101": 0.0828857421875, "0110": 0.071044921875, "0111": 0.0457763671875, "1000": 0.079345703125, "1001": 0.0496826171875, "1010": 0.0460205078125, "1011": 0.066162109375, "1100": 0.072265625, "1101": 0.0455322265625, "1110": 0.0528564453125, "1111": 0.0726318359375}, "5": {"0000": 0.0557861328125, "0001": 0.0706787109375, "0010": 0.0709228515625, "0011": 0.0567626953125, "0100": 0.05859375, "0101": 0.07373046875, "0110": 0.0665283203125, "0111": 0.054443359375, "1000": 0.07421875, "1001": 0.0546875, "1010": 0.050048828125, "1011": 0.0693359375, "1100": 0.068115234375, "1101": 0.0540771484375, "1110": 0.053955078125, "1111": 0.068115234375}}</t>
         </is>
       </c>
     </row>
@@ -2432,7 +3112,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C32" t="b">
@@ -2453,23 +3133,23 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8856964111328125</v>
+        <v>0.9082489013671872</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8841485129380275</v>
+        <v>0.9066690846862311</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1145629882812498</v>
+        <v>0.09255981445312439</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8856964111328125</v>
+        <v>0.9082489013671872</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1143035888671876</v>
+        <v>0.09175109863281278</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.097900390625, "0001": 0.10302734375, "0010": 0.0267333984375, "0011": 0.0277099609375, "0100": 0.028564453125, "0101": 0.028076171875, "0110": 0.0997314453125, "0111": 0.0950927734375, "1000": 0.1016845703125, "1001": 0.0968017578125, "1010": 0.0255126953125, "1011": 0.03369140625, "1100": 0.0244140625, "1101": 0.0238037109375, "1110": 0.0911865234375, "1111": 0.0960693359375}, "3": {"0000": 0.08935546875, "0001": 0.081787109375, "0010": 0.0506591796875, "0011": 0.0423583984375, "0100": 0.04833984375, "0101": 0.0487060546875, "0110": 0.0853271484375, "0111": 0.072021484375, "1000": 0.0760498046875, "1001": 0.0780029296875, "1010": 0.0472412109375, "1011": 0.0404052734375, "1100": 0.0460205078125, "1101": 0.0413818359375, "1110": 0.080078125, "1111": 0.072265625}, "5": {"0000": 0.0709228515625, "0001": 0.0706787109375, "0010": 0.0589599609375, "0011": 0.05029296875, "0100": 0.053955078125, "0101": 0.05419921875, "0110": 0.0711669921875, "0111": 0.07666015625, "1000": 0.0791015625, "1001": 0.068359375, "1010": 0.0484619140625, "1011": 0.0552978515625, "1100": 0.0560302734375, "1101": 0.0521240234375, "1110": 0.0682373046875, "1111": 0.0655517578125}}</t>
+          <t>{"1": {"0000": 0.098876953125, "0001": 0.09912109375, "0010": 0.0274658203125, "0011": 0.0308837890625, "0100": 0.0333251953125, "0101": 0.028076171875, "0110": 0.0947265625, "0111": 0.0921630859375, "1000": 0.0980224609375, "1001": 0.102294921875, "1010": 0.0325927734375, "1011": 0.0264892578125, "1100": 0.0274658203125, "1101": 0.0274658203125, "1110": 0.095947265625, "1111": 0.0850830078125}, "3": {"0000": 0.07470703125, "0001": 0.073486328125, "0010": 0.0523681640625, "0011": 0.0482177734375, "0100": 0.056396484375, "0101": 0.0533447265625, "0110": 0.073974609375, "0111": 0.068603515625, "1000": 0.0738525390625, "1001": 0.072021484375, "1010": 0.0576171875, "1011": 0.046630859375, "1100": 0.0556640625, "1101": 0.04931640625, "1110": 0.072265625, "1111": 0.071533203125}, "5": {"0000": 0.066650390625, "0001": 0.0694580078125, "0010": 0.0626220703125, "0011": 0.0615234375, "0100": 0.0621337890625, "0101": 0.059326171875, "0110": 0.0645751953125, "0111": 0.06787109375, "1000": 0.06884765625, "1001": 0.0640869140625, "1010": 0.0579833984375, "1011": 0.0567626953125, "1100": 0.05322265625, "1101": 0.060791015625, "1110": 0.064453125, "1111": 0.0596923828125}}</t>
         </is>
       </c>
     </row>
@@ -2481,7 +3161,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C33" t="b">
@@ -2502,23 +3182,23 @@
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8434295654296874</v>
+        <v>0.8276672363281249</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8422529275786478</v>
+        <v>0.8258595475027087</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1565704345703124</v>
+        <v>0.1723327636718741</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8434295654296874</v>
+        <v>0.8276672363281249</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1565704345703127</v>
+        <v>0.1723327636718752</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.1024169921875, "0001": 0.030029296875, "0010": 0.090576171875, "0011": 0.0286865234375, "0100": 0.030517578125, "0101": 0.0965576171875, "0110": 0.0321044921875, "0111": 0.09228515625, "1000": 0.092529296875, "1001": 0.02685546875, "1010": 0.09521484375, "1011": 0.0345458984375, "1100": 0.0302734375, "1101": 0.0902099609375, "1110": 0.03271484375, "1111": 0.094482421875}, "3": {"0000": 0.086181640625, "0001": 0.0435791015625, "0010": 0.081298828125, "0011": 0.0445556640625, "0100": 0.0546875, "0101": 0.0792236328125, "0110": 0.044677734375, "0111": 0.0765380859375, "1000": 0.082763671875, "1001": 0.0465087890625, "1010": 0.0723876953125, "1011": 0.04345703125, "1100": 0.05078125, "1101": 0.0771484375, "1110": 0.0458984375, "1111": 0.0703125}, "5": {"0000": 0.074951171875, "0001": 0.056396484375, "0010": 0.0751953125, "0011": 0.0550537109375, "0100": 0.0592041015625, "0101": 0.06982421875, "0110": 0.0537109375, "0111": 0.067626953125, "1000": 0.0706787109375, "1001": 0.054443359375, "1010": 0.0726318359375, "1011": 0.05126953125, "1100": 0.053466796875, "1101": 0.063720703125, "1110": 0.052490234375, "1111": 0.0693359375}}</t>
+          <t>{"1": {"0000": 0.09619140625, "0001": 0.037353515625, "0010": 0.0823974609375, "0011": 0.03466796875, "0100": 0.0328369140625, "0101": 0.087890625, "0110": 0.0361328125, "0111": 0.0914306640625, "1000": 0.0892333984375, "1001": 0.0338134765625, "1010": 0.094970703125, "1011": 0.0361328125, "1100": 0.0335693359375, "1101": 0.0924072265625, "1110": 0.0364990234375, "1111": 0.08447265625}, "3": {"0000": 0.0714111328125, "0001": 0.05517578125, "0010": 0.07568359375, "0011": 0.05322265625, "0100": 0.057861328125, "0101": 0.0697021484375, "0110": 0.0599365234375, "0111": 0.072265625, "1000": 0.0673828125, "1001": 0.0498046875, "1010": 0.0716552734375, "1011": 0.055419921875, "1100": 0.051025390625, "1101": 0.072021484375, "1110": 0.0498046875, "1111": 0.067626953125}, "5": {"0000": 0.0662841796875, "0001": 0.0662841796875, "0010": 0.0618896484375, "0011": 0.059814453125, "0100": 0.062255859375, "0101": 0.0572509765625, "0110": 0.06201171875, "0111": 0.0699462890625, "1000": 0.0623779296875, "1001": 0.059814453125, "1010": 0.0592041015625, "1011": 0.0609130859375, "1100": 0.061279296875, "1101": 0.0638427734375, "1110": 0.06298828125, "1111": 0.0638427734375}}</t>
         </is>
       </c>
     </row>
@@ -2530,7 +3210,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C34" t="b">
@@ -2551,23 +3231,23 @@
         <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9052734374999998</v>
+        <v>0.8629455566406249</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9038506913556328</v>
+        <v>0.8617963864642667</v>
       </c>
       <c r="J34" t="n">
-        <v>0.09539794921874978</v>
+        <v>0.137054443359374</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9052734374999998</v>
+        <v>0.8629455566406249</v>
       </c>
       <c r="L34" t="n">
-        <v>0.09472656250000019</v>
+        <v>0.1370544433593752</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.029052734375, "0001": 0.1024169921875, "0010": 0.1024169921875, "0011": 0.025390625, "0100": 0.1009521484375, "0101": 0.0286865234375, "0110": 0.0291748046875, "0111": 0.1009521484375, "1000": 0.0250244140625, "1001": 0.1038818359375, "1010": 0.0904541015625, "1011": 0.02099609375, "1100": 0.0992431640625, "1101": 0.0242919921875, "1110": 0.0242919921875, "1111": 0.0927734375}, "3": {"0000": 0.049072265625, "0001": 0.08154296875, "0010": 0.08251953125, "0011": 0.0455322265625, "0100": 0.0804443359375, "0101": 0.0462646484375, "0110": 0.048583984375, "0111": 0.0821533203125, "1000": 0.0465087890625, "1001": 0.07568359375, "1010": 0.081298828125, "1011": 0.0400390625, "1100": 0.0810546875, "1101": 0.03857421875, "1110": 0.045654296875, "1111": 0.0750732421875}, "5": {"0000": 0.055419921875, "0001": 0.075439453125, "0010": 0.07861328125, "0011": 0.0479736328125, "0100": 0.07958984375, "0101": 0.0548095703125, "0110": 0.052490234375, "0111": 0.0714111328125, "1000": 0.0537109375, "1001": 0.0679931640625, "1010": 0.0733642578125, "1011": 0.0499267578125, "1100": 0.06787109375, "1101": 0.0528564453125, "1110": 0.0516357421875, "1111": 0.06689453125}}</t>
+          <t>{"1": {"0000": 0.0335693359375, "0001": 0.0936279296875, "0010": 0.095703125, "0011": 0.0313720703125, "0100": 0.0943603515625, "0101": 0.031494140625, "0110": 0.02734375, "0111": 0.09716796875, "1000": 0.02783203125, "1001": 0.088623046875, "1010": 0.098876953125, "1011": 0.0286865234375, "1100": 0.0966796875, "1101": 0.0322265625, "1110": 0.028564453125, "1111": 0.0938720703125}, "3": {"0000": 0.05078125, "0001": 0.0771484375, "0010": 0.081298828125, "0011": 0.044677734375, "0100": 0.0809326171875, "0101": 0.050048828125, "0110": 0.0535888671875, "0111": 0.0771484375, "1000": 0.0516357421875, "1001": 0.076904296875, "1010": 0.0772705078125, "1011": 0.0482177734375, "1100": 0.0657958984375, "1101": 0.0439453125, "1110": 0.0504150390625, "1111": 0.0701904296875}, "5": {"0000": 0.062744140625, "0001": 0.068603515625, "0010": 0.0684814453125, "0011": 0.06103515625, "0100": 0.069091796875, "0101": 0.0574951171875, "0110": 0.0531005859375, "0111": 0.06640625, "1000": 0.05908203125, "1001": 0.0655517578125, "1010": 0.059814453125, "1011": 0.0626220703125, "1100": 0.0595703125, "1101": 0.0550537109375, "1110": 0.0599365234375, "1111": 0.0714111328125}}</t>
         </is>
       </c>
     </row>
@@ -2579,7 +3259,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C35" t="b">
@@ -2600,23 +3280,23 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9038696289062498</v>
+        <v>0.9174194335937498</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9027225912130573</v>
+        <v>0.9146412681955125</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1013641357421873</v>
+        <v>0.09608459472656233</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9038696289062498</v>
+        <v>0.9174194335937498</v>
       </c>
       <c r="L35" t="n">
-        <v>0.09613037109375021</v>
+        <v>0.08258056640625026</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.1033935546875, "0001": 0.09814453125, "0010": 0.0264892578125, "0011": 0.02490234375, "0100": 0.0272216796875, "0101": 0.026611328125, "0110": 0.1002197265625, "0111": 0.091064453125, "1000": 0.02685546875, "1001": 0.025634765625, "1010": 0.096435546875, "1011": 0.096923828125, "1100": 0.108154296875, "1101": 0.0980224609375, "1110": 0.026123046875, "1111": 0.0238037109375}, "3": {"0000": 0.0885009765625, "0001": 0.0810546875, "0010": 0.044189453125, "0011": 0.042724609375, "0100": 0.0556640625, "0101": 0.0478515625, "0110": 0.0792236328125, "0111": 0.075927734375, "1000": 0.04931640625, "1001": 0.044921875, "1010": 0.0791015625, "1011": 0.06982421875, "1100": 0.079833984375, "1101": 0.078125, "1110": 0.0419921875, "1111": 0.041748046875}, "5": {"0000": 0.0789794921875, "0001": 0.0721435546875, "0010": 0.0579833984375, "0011": 0.0546875, "0100": 0.0557861328125, "0101": 0.0587158203125, "0110": 0.072265625, "0111": 0.06640625, "1000": 0.0594482421875, "1001": 0.055908203125, "1010": 0.0694580078125, "1011": 0.0615234375, "1100": 0.0726318359375, "1101": 0.0604248046875, "1110": 0.05224609375, "1111": 0.0513916015625}}</t>
+          <t>{"1": {"0000": 0.0904541015625, "0001": 0.105712890625, "0010": 0.0260009765625, "0011": 0.028564453125, "0100": 0.0303955078125, "0101": 0.0291748046875, "0110": 0.10791015625, "0111": 0.091064453125, "1000": 0.027099609375, "1001": 0.0283203125, "1010": 0.0941162109375, "1011": 0.1029052734375, "1100": 0.097412109375, "1101": 0.0904541015625, "1110": 0.0252685546875, "1111": 0.025146484375}, "3": {"0000": 0.07763671875, "0001": 0.077392578125, "0010": 0.05126953125, "0011": 0.0509033203125, "0100": 0.052001953125, "0101": 0.050048828125, "0110": 0.076416015625, "0111": 0.0775146484375, "1000": 0.05322265625, "1001": 0.04638671875, "1010": 0.07275390625, "1011": 0.07177734375, "1100": 0.0770263671875, "1101": 0.0692138671875, "1110": 0.0479736328125, "1111": 0.0484619140625}, "5": {"0000": 0.0701904296875, "0001": 0.0673828125, "0010": 0.0584716796875, "0011": 0.0556640625, "0100": 0.0615234375, "0101": 0.057861328125, "0110": 0.0704345703125, "0111": 0.063232421875, "1000": 0.05859375, "1001": 0.0538330078125, "1010": 0.06787109375, "1011": 0.0675048828125, "1100": 0.069580078125, "1101": 0.0692138671875, "1110": 0.0552978515625, "1111": 0.0533447265625}}</t>
         </is>
       </c>
     </row>
@@ -2628,7 +3308,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C36" t="b">
@@ -2649,23 +3329,23 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>0.811767578125</v>
+        <v>0.8431854248046873</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8111538961018135</v>
+        <v>0.8428164282549437</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1882324218749997</v>
+        <v>0.1568145751953114</v>
       </c>
       <c r="K36" t="n">
-        <v>0.811767578125</v>
+        <v>0.8431854248046873</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1882324218750001</v>
+        <v>0.1568145751953127</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.0970458984375, "0001": 0.032470703125, "0010": 0.0885009765625, "0011": 0.031005859375, "0100": 0.036865234375, "0101": 0.0947265625, "0110": 0.03564453125, "0111": 0.087158203125, "1000": 0.03759765625, "1001": 0.09130859375, "1010": 0.035888671875, "1011": 0.0902099609375, "1100": 0.0887451171875, "1101": 0.0343017578125, "1110": 0.0872802734375, "1111": 0.03125}, "3": {"0000": 0.083740234375, "0001": 0.0482177734375, "0010": 0.076904296875, "0011": 0.047607421875, "0100": 0.0567626953125, "0101": 0.0738525390625, "0110": 0.050048828125, "0111": 0.0750732421875, "1000": 0.04833984375, "1001": 0.07861328125, "1010": 0.047119140625, "1011": 0.0699462890625, "1100": 0.0782470703125, "1101": 0.0452880859375, "1110": 0.073974609375, "1111": 0.0462646484375}, "5": {"0000": 0.078857421875, "0001": 0.055908203125, "0010": 0.0721435546875, "0011": 0.0513916015625, "0100": 0.0523681640625, "0101": 0.0704345703125, "0110": 0.0592041015625, "0111": 0.076416015625, "1000": 0.053955078125, "1001": 0.069091796875, "1010": 0.051025390625, "1011": 0.06640625, "1100": 0.07177734375, "1101": 0.0506591796875, "1110": 0.0692138671875, "1111": 0.0511474609375}}</t>
+          <t>{"1": {"0000": 0.0958251953125, "0001": 0.03076171875, "0010": 0.096435546875, "0011": 0.0325927734375, "0100": 0.036865234375, "0101": 0.091796875, "0110": 0.03125, "0111": 0.0941162109375, "1000": 0.0316162109375, "1001": 0.0909423828125, "1010": 0.034423828125, "1011": 0.0885009765625, "1100": 0.0899658203125, "1101": 0.0345458984375, "1110": 0.0877685546875, "1111": 0.0325927734375}, "3": {"0000": 0.0811767578125, "0001": 0.05126953125, "0010": 0.07666015625, "0011": 0.0550537109375, "0100": 0.0528564453125, "0101": 0.0780029296875, "0110": 0.05078125, "0111": 0.0689697265625, "1000": 0.0496826171875, "1001": 0.07470703125, "1010": 0.05224609375, "1011": 0.0712890625, "1100": 0.0703125, "1101": 0.046630859375, "1110": 0.0697021484375, "1111": 0.0506591796875}, "5": {"0000": 0.070556640625, "0001": 0.0616455078125, "0010": 0.068115234375, "0011": 0.0582275390625, "0100": 0.0595703125, "0101": 0.069091796875, "0110": 0.0531005859375, "0111": 0.0623779296875, "1000": 0.0543212890625, "1001": 0.07080078125, "1010": 0.05712890625, "1011": 0.06591796875, "1100": 0.07080078125, "1101": 0.058837890625, "1110": 0.0634765625, "1111": 0.0560302734375}}</t>
         </is>
       </c>
     </row>
@@ -2677,7 +3357,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C37" t="b">
@@ -2698,23 +3378,3551 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8708038330078122</v>
+        <v>0.86468505859375</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8704809061010826</v>
+        <v>0.8626341423951628</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1291961669921874</v>
+        <v>0.1353149414062488</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8708038330078122</v>
+        <v>0.86468505859375</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1291961669921877</v>
+        <v>0.1353149414062502</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{"1": {"0000": 0.0279541015625, "0001": 0.10302734375, "0010": 0.097412109375, "0011": 0.026611328125, "0100": 0.09423828125, "0101": 0.0267333984375, "0110": 0.0286865234375, "0111": 0.09619140625, "1000": 0.10302734375, "1001": 0.02783203125, "1010": 0.027099609375, "1011": 0.094970703125, "1100": 0.0301513671875, "1101": 0.0977783203125, "1110": 0.0936279296875, "1111": 0.024658203125}, "3": {"0000": 0.04736328125, "0001": 0.0867919921875, "0010": 0.0863037109375, "0011": 0.0401611328125, "0100": 0.085693359375, "0101": 0.0413818359375, "0110": 0.044189453125, "0111": 0.078857421875, "1000": 0.0863037109375, "1001": 0.0443115234375, "1010": 0.0445556640625, "1011": 0.07568359375, "1100": 0.04248046875, "1101": 0.0830078125, "1110": 0.0743408203125, "1111": 0.03857421875}, "5": {"0000": 0.0545654296875, "0001": 0.076904296875, "0010": 0.0843505859375, "0011": 0.0499267578125, "0100": 0.0799560546875, "0101": 0.0489501953125, "0110": 0.0472412109375, "0111": 0.072265625, "1000": 0.071533203125, "1001": 0.0472412109375, "1010": 0.04833984375, "1011": 0.0736083984375, "1100": 0.0506591796875, "1101": 0.0753173828125, "1110": 0.0767822265625, "1111": 0.0423583984375}}</t>
+          <t>{"1": {"0000": 0.026123046875, "0001": 0.0958251953125, "0010": 0.08984375, "0011": 0.0279541015625, "0100": 0.0953369140625, "0101": 0.0252685546875, "0110": 0.030517578125, "0111": 0.101806640625, "1000": 0.097412109375, "1001": 0.02880859375, "1010": 0.026611328125, "1011": 0.0999755859375, "1100": 0.0289306640625, "1101": 0.09423828125, "1110": 0.1029052734375, "1111": 0.0284423828125}, "3": {"0000": 0.05029296875, "0001": 0.088623046875, "0010": 0.085205078125, "0011": 0.04296875, "0100": 0.0853271484375, "0101": 0.0460205078125, "0110": 0.0447998046875, "0111": 0.0819091796875, "1000": 0.0821533203125, "1001": 0.042236328125, "1010": 0.0386962890625, "1011": 0.0794677734375, "1100": 0.0469970703125, "1101": 0.07373046875, "1110": 0.076416015625, "1111": 0.03515625}, "5": {"0000": 0.0540771484375, "0001": 0.072509765625, "0010": 0.0782470703125, "0011": 0.0550537109375, "0100": 0.0791015625, "0101": 0.0548095703125, "0110": 0.0484619140625, "0111": 0.0748291015625, "1000": 0.07373046875, "1001": 0.0484619140625, "1010": 0.0472412109375, "1011": 0.0692138671875, "1100": 0.050048828125, "1101": 0.0740966796875, "1110": 0.073486328125, "1111": 0.046630859375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C38" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>R1C1</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9088134765625</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9084333815805491</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.09118652343749964</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.9088134765625</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.0911865234375</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>R1C2</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.80029296875</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8000912276281822</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1997070312499997</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.80029296875</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.19970703125</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>R1C3</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.804931640625</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8047908468418468</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.1950683593749996</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.804931640625</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.195068359375</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C41" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>R2C1</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8175048828125</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8172062715391107</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.1824951171874996</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.8175048828125</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1824951171875</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.779296875</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7788103642190057</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.2207031249999997</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.779296875</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.220703125</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C43" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.781982421875</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.781617497057246</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.2180175781249996</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.781982421875</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.218017578125</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>R3C1</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.81298828125</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.812616740105401</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.1870117187499995</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.81298828125</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.18701171875</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C45" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.7708740234375</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.770563660105268</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.2291259765624995</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.7708740234375</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.2291259765625</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C46" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>R3C3</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.7921142578125</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.7920312989826931</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.2078857421874995</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.7921142578125</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.2078857421875</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C47" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>R1C1</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.901123046875</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.9007663871213817</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.098876953124999</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.901123046875</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.098876953125</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C48" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>R1C2</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.7373046875</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7370796954745664</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.2626953124999991</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.7373046875</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.2626953125</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C49" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>R1C3</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.7425537109375</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.741615358266981</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.2574462890624991</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.7425537109375</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2574462890625</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C50" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>R2C1</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.759521484375</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.7591506024763466</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.240478515624999</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.759521484375</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.240478515625</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C51" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.697265625</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.6969438138536428</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.3027343749999991</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.697265625</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.302734375</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C52" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.7244873046875</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.7241670256916264</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.2755126953124991</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.7244873046875</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.2755126953125</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C53" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>R3C1</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.7532958984375</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.7528250444905603</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.2467041015624989</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.7532958984375</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.2467041015625</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C54" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.720458984375</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.7201124755106604</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.2795410156249989</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.720458984375</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.279541015625</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C55" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>R3C3</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.7703857421875</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.7699711813359512</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.2296142578124989</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.7703857421875</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.2296142578125</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C56" t="b">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>R1C1</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.9501800537109375</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9489005162235796</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.05986022949218738</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.9501800537109375</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.0498199462890625</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.116943359375, "0001": 0.1136474609375, "0010": 0.01025390625, "0011": 0.0118408203125, "0100": 0.123291015625, "0101": 0.1182861328125, "0110": 0.0111083984375, "0111": 0.0101318359375, "1000": 0.00927734375, "1001": 0.0086669921875, "1010": 0.10498046875, "1011": 0.1185302734375, "1100": 0.0106201171875, "1101": 0.010986328125, "1110": 0.1107177734375, "1111": 0.1107177734375}, "3": {"0000": 0.1148681640625, "0001": 0.1107177734375, "0010": 0.013671875, "0011": 0.017333984375, "0100": 0.1197509765625, "0101": 0.10595703125, "0110": 0.017333984375, "0111": 0.018310546875, "1000": 0.016845703125, "1001": 0.0174560546875, "1010": 0.107421875, "1011": 0.1051025390625, "1100": 0.0150146484375, "1101": 0.0164794921875, "1110": 0.10546875, "1111": 0.0982666015625}, "5": {"0000": 0.1121826171875, "0001": 0.106201171875, "0010": 0.02001953125, "0011": 0.0184326171875, "0100": 0.10498046875, "0101": 0.1063232421875, "0110": 0.0205078125, "0111": 0.0218505859375, "1000": 0.0172119140625, "1001": 0.020263671875, "1010": 0.1031494140625, "1011": 0.1065673828125, "1100": 0.0213623046875, "1101": 0.020263671875, "1110": 0.107177734375, "1111": 0.093505859375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C57" t="b">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>R1C2</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.8753051757812501</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.874806987388897</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.1246948242187497</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.8753051757812501</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1246948242187501</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.102783203125, "0001": 0.0303955078125, "0010": 0.0968017578125, "0011": 0.02734375, "0100": 0.0982666015625, "0101": 0.029296875, "0110": 0.09912109375, "0111": 0.0250244140625, "1000": 0.0250244140625, "1001": 0.0977783203125, "1010": 0.02392578125, "1011": 0.10009765625, "1100": 0.024658203125, "1101": 0.0966796875, "1110": 0.0245361328125, "1111": 0.0982666015625}, "3": {"0000": 0.0865478515625, "0001": 0.0423583984375, "0010": 0.0819091796875, "0011": 0.04248046875, "0100": 0.08984375, "0101": 0.0465087890625, "0110": 0.08251953125, "0111": 0.0421142578125, "1000": 0.0400390625, "1001": 0.0843505859375, "1010": 0.043701171875, "1011": 0.0745849609375, "1100": 0.0416259765625, "1101": 0.0753173828125, "1110": 0.0421142578125, "1111": 0.083984375}, "5": {"0000": 0.071533203125, "0001": 0.0567626953125, "0010": 0.077392578125, "0011": 0.0518798828125, "0100": 0.082275390625, "0101": 0.0556640625, "0110": 0.0706787109375, "0111": 0.0501708984375, "1000": 0.0528564453125, "1001": 0.0723876953125, "1010": 0.0487060546875, "1011": 0.0675048828125, "1100": 0.050537109375, "1101": 0.0723876953125, "1110": 0.0513916015625, "1111": 0.06787109375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C58" t="b">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>R1C3</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.8810882568359373</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.8802517982690889</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.1189117431640623</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.8810882568359373</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1189117431640626</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.024658203125, "0001": 0.0987548828125, "0010": 0.10302734375, "0011": 0.0277099609375, "0100": 0.026123046875, "0101": 0.0987548828125, "0110": 0.095703125, "0111": 0.03076171875, "1000": 0.0963134765625, "1001": 0.0245361328125, "1010": 0.0262451171875, "1011": 0.1025390625, "1100": 0.0950927734375, "1101": 0.0235595703125, "1110": 0.0260009765625, "1111": 0.1002197265625}, "3": {"0000": 0.0482177734375, "0001": 0.0841064453125, "0010": 0.0838623046875, "0011": 0.04052734375, "0100": 0.0479736328125, "0101": 0.0816650390625, "0110": 0.083984375, "0111": 0.038330078125, "1000": 0.0848388671875, "1001": 0.0384521484375, "1010": 0.0440673828125, "1011": 0.0770263671875, "1100": 0.0806884765625, "1101": 0.0421142578125, "1110": 0.0428466796875, "1111": 0.081298828125}, "5": {"0000": 0.0545654296875, "0001": 0.076171875, "0010": 0.0791015625, "0011": 0.0526123046875, "0100": 0.0516357421875, "0101": 0.070068359375, "0110": 0.0814208984375, "0111": 0.0499267578125, "1000": 0.07177734375, "1001": 0.051513671875, "1010": 0.04931640625, "1011": 0.0728759765625, "1100": 0.071533203125, "1101": 0.04833984375, "1110": 0.052978515625, "1111": 0.066162109375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C59" t="b">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>R2C1</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.93609619140625</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.9355207030188646</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.06617736816406233</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.93609619140625</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.06390380859375012</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.1011962890625, "0001": 0.1025390625, "0010": 0.0218505859375, "0011": 0.0213623046875, "0100": 0.020263671875, "0101": 0.0220947265625, "0110": 0.1109619140625, "0111": 0.10693359375, "1000": 0.1031494140625, "1001": 0.099853515625, "1010": 0.022216796875, "1011": 0.0196533203125, "1100": 0.025390625, "1101": 0.0201416015625, "1110": 0.096923828125, "1111": 0.10546875}, "3": {"0000": 0.0870361328125, "0001": 0.084228515625, "0010": 0.04248046875, "0011": 0.041015625, "0100": 0.0455322265625, "0101": 0.044189453125, "0110": 0.09326171875, "0111": 0.08349609375, "1000": 0.082763671875, "1001": 0.0792236328125, "1010": 0.0445556640625, "1011": 0.0406494140625, "1100": 0.040283203125, "1101": 0.03564453125, "1110": 0.078125, "1111": 0.0775146484375}, "5": {"0000": 0.0755615234375, "0001": 0.06787109375, "0010": 0.05224609375, "0011": 0.0506591796875, "0100": 0.05712890625, "0101": 0.0574951171875, "0110": 0.080078125, "0111": 0.0677490234375, "1000": 0.07421875, "1001": 0.073486328125, "1010": 0.0494384765625, "1011": 0.0509033203125, "1100": 0.05029296875, "1101": 0.0518798828125, "1110": 0.070556640625, "1111": 0.0704345703125}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C60" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.8572082519531251</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.856341452099041</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.1427917480468748</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.8572082519531251</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.1427917480468752</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.10107421875, "0001": 0.030029296875, "0010": 0.0931396484375, "0011": 0.0277099609375, "0100": 0.031005859375, "0101": 0.096923828125, "0110": 0.0274658203125, "0111": 0.0987548828125, "1000": 0.09326171875, "1001": 0.0250244140625, "1010": 0.091796875, "1011": 0.02783203125, "1100": 0.029541015625, "1101": 0.100830078125, "1110": 0.0299072265625, "1111": 0.095703125}, "3": {"0000": 0.0926513671875, "0001": 0.04345703125, "0010": 0.0872802734375, "0011": 0.0450439453125, "0100": 0.042236328125, "0101": 0.088623046875, "0110": 0.04833984375, "0111": 0.08154296875, "1000": 0.0782470703125, "1001": 0.044189453125, "1010": 0.07177734375, "1011": 0.041259765625, "1100": 0.0400390625, "1101": 0.0810546875, "1110": 0.0421142578125, "1111": 0.0721435546875}, "5": {"0000": 0.0782470703125, "0001": 0.0501708984375, "0010": 0.0810546875, "0011": 0.050048828125, "0100": 0.05322265625, "0101": 0.076904296875, "0110": 0.0511474609375, "0111": 0.07421875, "1000": 0.075439453125, "1001": 0.0447998046875, "1010": 0.0770263671875, "1011": 0.0467529296875, "1100": 0.052001953125, "1101": 0.07421875, "1110": 0.045654296875, "1111": 0.069091796875}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C61" t="b">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.8883361816406248</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.8870149239685996</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.1133422851562499</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.8883361816406248</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.1116638183593752</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.028076171875, "0001": 0.0982666015625, "0010": 0.103271484375, "0011": 0.029541015625, "0100": 0.1019287109375, "0101": 0.02490234375, "0110": 0.0228271484375, "0111": 0.1041259765625, "1000": 0.0272216796875, "1001": 0.096435546875, "1010": 0.096435546875, "1011": 0.0286865234375, "1100": 0.09130859375, "1101": 0.0272216796875, "1110": 0.0240478515625, "1111": 0.095703125}, "3": {"0000": 0.0452880859375, "0001": 0.083251953125, "0010": 0.083984375, "0011": 0.0452880859375, "0100": 0.08642578125, "0101": 0.0440673828125, "0110": 0.041259765625, "0111": 0.077880859375, "1000": 0.0474853515625, "1001": 0.0772705078125, "1010": 0.08056640625, "1011": 0.0408935546875, "1100": 0.0838623046875, "1101": 0.0469970703125, "1110": 0.0390625, "1111": 0.076416015625}, "5": {"0000": 0.05517578125, "0001": 0.0723876953125, "0010": 0.0802001953125, "0011": 0.0491943359375, "0100": 0.0792236328125, "0101": 0.0511474609375, "0110": 0.0516357421875, "0111": 0.0767822265625, "1000": 0.0535888671875, "1001": 0.068359375, "1010": 0.072021484375, "1011": 0.0445556640625, "1100": 0.0771484375, "1101": 0.0467529296875, "1110": 0.0509033203125, "1111": 0.0709228515625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C62" t="b">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>R3C1</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.8881988525390624</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.8875250956707144</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.1118011474609371</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.8881988525390624</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.1118011474609376</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.10205078125, "0001": 0.103271484375, "0010": 0.024169921875, "0011": 0.0272216796875, "0100": 0.0240478515625, "0101": 0.0240478515625, "0110": 0.099609375, "0111": 0.0997314453125, "1000": 0.0238037109375, "1001": 0.0235595703125, "1010": 0.0963134765625, "1011": 0.10400390625, "1100": 0.103759765625, "1101": 0.098876953125, "1110": 0.0220947265625, "1111": 0.0234375}, "3": {"0000": 0.0906982421875, "0001": 0.0870361328125, "0010": 0.042236328125, "0011": 0.039306640625, "0100": 0.0435791015625, "0101": 0.0421142578125, "0110": 0.08251953125, "0111": 0.086669921875, "1000": 0.040283203125, "1001": 0.037841796875, "1010": 0.085693359375, "1011": 0.080078125, "1100": 0.0887451171875, "1101": 0.0789794921875, "1110": 0.038330078125, "1111": 0.035888671875}, "5": {"0000": 0.07958984375, "0001": 0.072021484375, "0010": 0.0504150390625, "0011": 0.044921875, "0100": 0.0546875, "0101": 0.0533447265625, "0110": 0.0814208984375, "0111": 0.07568359375, "1000": 0.0533447265625, "1001": 0.0509033203125, "1010": 0.068115234375, "1011": 0.0694580078125, "1100": 0.0780029296875, "1101": 0.07421875, "1110": 0.0445556640625, "1111": 0.04931640625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C63" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.8561553955078124</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8552513333721051</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.1438446044921871</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.8561553955078124</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1438446044921876</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.099609375, "0001": 0.030029296875, "0010": 0.099609375, "0011": 0.0311279296875, "0100": 0.0277099609375, "0101": 0.0916748046875, "0110": 0.0333251953125, "0111": 0.0968017578125, "1000": 0.026123046875, "1001": 0.0947265625, "1010": 0.0294189453125, "1011": 0.0924072265625, "1100": 0.0980224609375, "1101": 0.029296875, "1110": 0.0911865234375, "1111": 0.0289306640625}, "3": {"0000": 0.083740234375, "0001": 0.0478515625, "0010": 0.079833984375, "0011": 0.0489501953125, "0100": 0.0518798828125, "0101": 0.0819091796875, "0110": 0.05078125, "0111": 0.0789794921875, "1000": 0.044677734375, "1001": 0.078857421875, "1010": 0.0426025390625, "1011": 0.0740966796875, "1100": 0.0743408203125, "1101": 0.040283203125, "1110": 0.078125, "1111": 0.0430908203125}, "5": {"0000": 0.0789794921875, "0001": 0.0540771484375, "0010": 0.07763671875, "0011": 0.052734375, "0100": 0.0555419921875, "0101": 0.07275390625, "0110": 0.0540771484375, "0111": 0.071533203125, "1000": 0.0562744140625, "1001": 0.069580078125, "1010": 0.0567626953125, "1011": 0.063720703125, "1100": 0.0643310546875, "1101": 0.054931640625, "1110": 0.06396484375, "1111": 0.0531005859375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C64" t="b">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>R3C3</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.8806610107421874</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.8790722502090546</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.1193389892578121</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.8806610107421874</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1193389892578127</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.0272216796875, "0001": 0.0997314453125, "0010": 0.0989990234375, "0011": 0.0264892578125, "0100": 0.10400390625, "0101": 0.0272216796875, "0110": 0.027587890625, "0111": 0.10302734375, "1000": 0.0909423828125, "1001": 0.02587890625, "1010": 0.0238037109375, "1011": 0.0987548828125, "1100": 0.0281982421875, "1101": 0.0916748046875, "1110": 0.1041259765625, "1111": 0.0223388671875}, "3": {"0000": 0.04736328125, "0001": 0.083251953125, "0010": 0.0916748046875, "0011": 0.04150390625, "0100": 0.08837890625, "0101": 0.0413818359375, "0110": 0.040283203125, "0111": 0.0802001953125, "1000": 0.084228515625, "1001": 0.040771484375, "1010": 0.0426025390625, "1011": 0.080322265625, "1100": 0.0382080078125, "1101": 0.0787353515625, "1110": 0.08251953125, "1111": 0.03857421875}, "5": {"0000": 0.0550537109375, "0001": 0.080322265625, "0010": 0.073974609375, "0011": 0.046875, "0100": 0.078857421875, "0101": 0.04541015625, "0110": 0.050537109375, "0111": 0.0750732421875, "1000": 0.079833984375, "1001": 0.049072265625, "1010": 0.0450439453125, "1011": 0.07666015625, "1100": 0.0447998046875, "1101": 0.07958984375, "1110": 0.078857421875, "1111": 0.0400390625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C65" t="b">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>R1C1</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.9434051513671875</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.9407070880186301</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.08164978027343722</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.9434051513671875</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.05659484863281253</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.109375, "0001": 0.110595703125, "0010": 0.0125732421875, "0011": 0.0108642578125, "0100": 0.11572265625, "0101": 0.10546875, "0110": 0.0115966796875, "0111": 0.0123291015625, "1000": 0.013671875, "1001": 0.0120849609375, "1010": 0.1121826171875, "1011": 0.1187744140625, "1100": 0.01171875, "1101": 0.0125732421875, "1110": 0.1121826171875, "1111": 0.1182861328125}, "3": {"0000": 0.1107177734375, "0001": 0.109619140625, "0010": 0.01904296875, "0011": 0.019287109375, "0100": 0.1009521484375, "0101": 0.10595703125, "0110": 0.0185546875, "0111": 0.021728515625, "1000": 0.0205078125, "1001": 0.02001953125, "1010": 0.1063232421875, "1011": 0.0960693359375, "1100": 0.0208740234375, "1101": 0.01953125, "1110": 0.1080322265625, "1111": 0.102783203125}, "5": {"0000": 0.1025390625, "0001": 0.1015625, "0010": 0.02490234375, "0011": 0.0228271484375, "0100": 0.106689453125, "0101": 0.1019287109375, "0110": 0.025390625, "0111": 0.0255126953125, "1000": 0.0240478515625, "1001": 0.0244140625, "1010": 0.1019287109375, "1011": 0.0994873046875, "1100": 0.0252685546875, "1101": 0.0233154296875, "1110": 0.0941162109375, "1111": 0.0960693359375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C66" t="b">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>R1C2</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.8780517578124998</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.8777972536358858</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.1219482421874993</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.8780517578124998</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1219482421875002</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.102783203125, "0001": 0.0299072265625, "0010": 0.0946044921875, "0011": 0.02880859375, "0100": 0.0955810546875, "0101": 0.0302734375, "0110": 0.096435546875, "0111": 0.02783203125, "1000": 0.0291748046875, "1001": 0.0963134765625, "1010": 0.02880859375, "1011": 0.0926513671875, "1100": 0.026123046875, "1101": 0.09619140625, "1110": 0.0322265625, "1111": 0.09228515625}, "3": {"0000": 0.0841064453125, "0001": 0.05029296875, "0010": 0.0816650390625, "0011": 0.0430908203125, "0100": 0.0802001953125, "0101": 0.0521240234375, "0110": 0.0777587890625, "0111": 0.0462646484375, "1000": 0.0496826171875, "1001": 0.0748291015625, "1010": 0.0484619140625, "1011": 0.0709228515625, "1100": 0.04345703125, "1101": 0.0780029296875, "1110": 0.0489501953125, "1111": 0.0701904296875}, "5": {"0000": 0.076904296875, "0001": 0.0614013671875, "0010": 0.076416015625, "0011": 0.051025390625, "0100": 0.071044921875, "0101": 0.0562744140625, "0110": 0.0703125, "0111": 0.05126953125, "1000": 0.05615234375, "1001": 0.068115234375, "1010": 0.0521240234375, "1011": 0.0704345703125, "1100": 0.054931640625, "1101": 0.0657958984375, "1110": 0.0506591796875, "1111": 0.067138671875}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C67" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>R1C3</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.8777008056640623</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.8768371176329258</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.1222991943359367</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.8777008056640623</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.1222991943359377</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.029296875, "0001": 0.0982666015625, "0010": 0.0986328125, "0011": 0.029541015625, "0100": 0.030029296875, "0101": 0.104736328125, "0110": 0.09326171875, "0111": 0.0252685546875, "1000": 0.1011962890625, "1001": 0.03076171875, "1010": 0.0283203125, "1011": 0.0911865234375, "1100": 0.0908203125, "1101": 0.026611328125, "1110": 0.0277099609375, "1111": 0.0943603515625}, "3": {"0000": 0.046630859375, "0001": 0.0791015625, "0010": 0.0823974609375, "0011": 0.0477294921875, "0100": 0.0523681640625, "0101": 0.0823974609375, "0110": 0.07470703125, "0111": 0.0457763671875, "1000": 0.0816650390625, "1001": 0.04833984375, "1010": 0.0443115234375, "1011": 0.0771484375, "1100": 0.0748291015625, "1101": 0.044189453125, "1110": 0.04541015625, "1111": 0.072998046875}, "5": {"0000": 0.0545654296875, "0001": 0.07275390625, "0010": 0.073974609375, "0011": 0.057373046875, "0100": 0.057861328125, "0101": 0.076171875, "0110": 0.06689453125, "0111": 0.052001953125, "1000": 0.07275390625, "1001": 0.0565185546875, "1010": 0.04833984375, "1011": 0.0621337890625, "1100": 0.0709228515625, "1101": 0.0533447265625, "1110": 0.0576171875, "1111": 0.0667724609375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C68" t="b">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>R2C1</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.8952484130859371</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.8949002235574931</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.1047515869140619</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.8952484130859371</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1047515869140628</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.096923828125, "0001": 0.098876953125, "0010": 0.0289306640625, "0011": 0.0318603515625, "0100": 0.0328369140625, "0101": 0.0318603515625, "0110": 0.0947265625, "0111": 0.0933837890625, "1000": 0.0963134765625, "1001": 0.0958251953125, "1010": 0.0340576171875, "1011": 0.0257568359375, "1100": 0.028076171875, "1101": 0.029541015625, "1110": 0.09375, "1111": 0.0872802734375}, "3": {"0000": 0.08154296875, "0001": 0.0736083984375, "0010": 0.0556640625, "0011": 0.0496826171875, "0100": 0.0552978515625, "0101": 0.049560546875, "0110": 0.078125, "0111": 0.07080078125, "1000": 0.0736083984375, "1001": 0.075927734375, "1010": 0.0513916015625, "1011": 0.0506591796875, "1100": 0.0511474609375, "1101": 0.0462646484375, "1110": 0.0692138671875, "1111": 0.0675048828125}, "5": {"0000": 0.0771484375, "0001": 0.0692138671875, "0010": 0.053955078125, "0011": 0.052490234375, "0100": 0.0538330078125, "0101": 0.056884765625, "0110": 0.0745849609375, "0111": 0.0654296875, "1000": 0.0760498046875, "1001": 0.0714111328125, "1010": 0.0533447265625, "1011": 0.052490234375, "1100": 0.0511474609375, "1101": 0.05615234375, "1110": 0.0662841796875, "1111": 0.069580078125}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C69" t="b">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.7903900146484373</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.7892130519969215</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.2096099853515616</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.7903900146484373</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.2096099853515626</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.092529296875, "0001": 0.0322265625, "0010": 0.088134765625, "0011": 0.0345458984375, "0100": 0.0350341796875, "0101": 0.09228515625, "0110": 0.03564453125, "0111": 0.091064453125, "1000": 0.0802001953125, "1001": 0.03955078125, "1010": 0.0960693359375, "1011": 0.0386962890625, "1100": 0.0374755859375, "1101": 0.09423828125, "1110": 0.0350341796875, "1111": 0.0772705078125}, "3": {"0000": 0.0830078125, "0001": 0.050537109375, "0010": 0.07568359375, "0011": 0.046630859375, "0100": 0.0518798828125, "0101": 0.076416015625, "0110": 0.0504150390625, "0111": 0.0743408203125, "1000": 0.0701904296875, "1001": 0.0513916015625, "1010": 0.0775146484375, "1011": 0.0489501953125, "1100": 0.0501708984375, "1101": 0.076171875, "1110": 0.05029296875, "1111": 0.06640625}, "5": {"0000": 0.0716552734375, "0001": 0.060302734375, "0010": 0.06884765625, "0011": 0.0601806640625, "0100": 0.05712890625, "0101": 0.07080078125, "0110": 0.055908203125, "0111": 0.0697021484375, "1000": 0.06689453125, "1001": 0.053955078125, "1010": 0.0654296875, "1011": 0.055419921875, "1100": 0.05517578125, "1101": 0.0665283203125, "1110": 0.0540771484375, "1111": 0.0679931640625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C70" t="b">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.8668212890624998</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.8662444114297827</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.1331787109374992</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.8668212890624998</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.1331787109375002</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.0284423828125, "0001": 0.093994140625, "0010": 0.097412109375, "0011": 0.028564453125, "0100": 0.098388671875, "0101": 0.03271484375, "0110": 0.0303955078125, "0111": 0.0953369140625, "1000": 0.0291748046875, "1001": 0.093994140625, "1010": 0.098388671875, "1011": 0.028076171875, "1100": 0.0931396484375, "1101": 0.0277099609375, "1110": 0.0303955078125, "1111": 0.0938720703125}, "3": {"0000": 0.051025390625, "0001": 0.0838623046875, "0010": 0.0755615234375, "0011": 0.0501708984375, "0100": 0.0762939453125, "0101": 0.0462646484375, "0110": 0.0501708984375, "0111": 0.076416015625, "1000": 0.0482177734375, "1001": 0.0762939453125, "1010": 0.0802001953125, "1011": 0.0450439453125, "1100": 0.0753173828125, "1101": 0.044189453125, "1110": 0.0460205078125, "1111": 0.074951171875}, "5": {"0000": 0.054443359375, "0001": 0.0703125, "0010": 0.069580078125, "0011": 0.0555419921875, "0100": 0.0750732421875, "0101": 0.0550537109375, "0110": 0.0562744140625, "0111": 0.067626953125, "1000": 0.0576171875, "1001": 0.0655517578125, "1010": 0.065185546875, "1011": 0.0577392578125, "1100": 0.0654296875, "1101": 0.0565185546875, "1110": 0.054931640625, "1111": 0.0731201171875}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C71" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>R3C1</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.8938140869140623</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.8913678286598843</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.1154785156249996</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.8938140869140623</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.1061859130859376</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.09619140625, "0001": 0.0926513671875, "0010": 0.0230712890625, "0011": 0.025146484375, "0100": 0.0279541015625, "0101": 0.0260009765625, "0110": 0.0975341796875, "0111": 0.1029052734375, "1000": 0.0279541015625, "1001": 0.028076171875, "1010": 0.09423828125, "1011": 0.1046142578125, "1100": 0.1011962890625, "1101": 0.0992431640625, "1110": 0.0257568359375, "1111": 0.0274658203125}, "3": {"0000": 0.0826416015625, "0001": 0.084716796875, "0010": 0.047119140625, "0011": 0.0465087890625, "0100": 0.0479736328125, "0101": 0.04443359375, "0110": 0.0791015625, "0111": 0.0751953125, "1000": 0.0482177734375, "1001": 0.0467529296875, "1010": 0.0782470703125, "1011": 0.0711669921875, "1100": 0.084228515625, "1101": 0.078369140625, "1110": 0.0399169921875, "1111": 0.04541015625}, "5": {"0000": 0.0738525390625, "0001": 0.0694580078125, "0010": 0.06103515625, "0011": 0.0550537109375, "0100": 0.0579833984375, "0101": 0.05712890625, "0110": 0.0654296875, "0111": 0.0714111328125, "1000": 0.05419921875, "1001": 0.0557861328125, "1010": 0.0673828125, "1011": 0.0703125, "1100": 0.0673828125, "1101": 0.067626953125, "1110": 0.052001953125, "1111": 0.053955078125}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C72" t="b">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.8681793212890624</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.8673859000206358</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.1318206787109367</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.8681793212890624</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.1318206787109378</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.09033203125, "0001": 0.031005859375, "0010": 0.093505859375, "0011": 0.0357666015625, "0100": 0.0350341796875, "0101": 0.08935546875, "0110": 0.0323486328125, "0111": 0.0972900390625, "1000": 0.032958984375, "1001": 0.0916748046875, "1010": 0.033935546875, "1011": 0.09423828125, "1100": 0.089111328125, "1101": 0.0328369140625, "1110": 0.085205078125, "1111": 0.035400390625}, "3": {"0000": 0.0693359375, "0001": 0.06201171875, "0010": 0.07177734375, "0011": 0.0555419921875, "0100": 0.05615234375, "0101": 0.0694580078125, "0110": 0.0548095703125, "0111": 0.0693359375, "1000": 0.0535888671875, "1001": 0.0697021484375, "1010": 0.0531005859375, "1011": 0.0709228515625, "1100": 0.069091796875, "1101": 0.052978515625, "1110": 0.0711669921875, "1111": 0.051025390625}, "5": {"0000": 0.0682373046875, "0001": 0.059814453125, "0010": 0.064697265625, "0011": 0.053955078125, "0100": 0.06396484375, "0101": 0.066650390625, "0110": 0.060302734375, "0111": 0.067626953125, "1000": 0.0562744140625, "1001": 0.0684814453125, "1010": 0.0538330078125, "1011": 0.061767578125, "1100": 0.0660400390625, "1101": 0.061279296875, "1110": 0.0673828125, "1111": 0.0596923828125}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C73" t="b">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>R3C3</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F73" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.8678131103515624</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.8659525228698639</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.1321868896484366</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.8678131103515624</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1321868896484376</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.0318603515625, "0001": 0.0994873046875, "0010": 0.0960693359375, "0011": 0.0247802734375, "0100": 0.099853515625, "0101": 0.0263671875, "0110": 0.0279541015625, "0111": 0.1005859375, "1000": 0.0943603515625, "1001": 0.0267333984375, "1010": 0.0234375, "1011": 0.1026611328125, "1100": 0.0252685546875, "1101": 0.091796875, "1110": 0.09814453125, "1111": 0.0306396484375}, "3": {"0000": 0.0472412109375, "0001": 0.0849609375, "0010": 0.0872802734375, "0011": 0.0382080078125, "0100": 0.08837890625, "0101": 0.04443359375, "0110": 0.04345703125, "0111": 0.080322265625, "1000": 0.0869140625, "1001": 0.044921875, "1010": 0.039306640625, "1011": 0.07958984375, "1100": 0.042236328125, "1101": 0.0823974609375, "1110": 0.07275390625, "1111": 0.03759765625}, "5": {"0000": 0.0518798828125, "0001": 0.08251953125, "0010": 0.078125, "0011": 0.048828125, "0100": 0.0770263671875, "0101": 0.05126953125, "0110": 0.046630859375, "0111": 0.0743408203125, "1000": 0.0704345703125, "1001": 0.04541015625, "1010": 0.0496826171875, "1011": 0.07470703125, "1100": 0.050537109375, "1101": 0.0738525390625, "1110": 0.0770263671875, "1111": 0.0477294921875}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C74" t="b">
+        <v>0</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>R1C1</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.912109375</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.9119987113489985</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.08789062499999982</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.912109375</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.087890625</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C75" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>R1C2</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.7772216796875</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.7770314732868681</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.2227783203124998</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.7772216796875</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2227783203125</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C76" t="b">
+        <v>0</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>R1C3</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.8079833984375</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.8077881590336866</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.1920166015624998</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.8079833984375</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.1920166015625</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C77" t="b">
+        <v>0</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>R2C1</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.8321533203125</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.831585174029924</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.1678466796874998</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.8321533203125</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.1678466796875</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.771728515625</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.7715213462478389</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.2282714843749998</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.771728515625</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.228271484375</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C79" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.7880859375</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.7875458248838094</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.2119140624999998</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.7880859375</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.2119140625</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C80" t="b">
+        <v>0</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>R3C1</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.795166015625</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.7950568538819395</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.2048339843749998</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.795166015625</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.204833984375</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C81" t="b">
+        <v>0</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.7569580078125</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.7566283332422161</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.2430419921874998</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.7569580078125</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.2430419921875</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C82" t="b">
+        <v>0</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>R3C3</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.7926025390625</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.7923946362091809</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.2073974609374998</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.7926025390625</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.2073974609375</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C83" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>R1C1</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.9078369140625</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.9077059824281528</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.09216308593749936</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.9078369140625</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.0921630859375</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C84" t="b">
+        <v>0</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>R1C2</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.762451171875</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.7623040533292981</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.2375488281249994</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.762451171875</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.237548828125</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>R1C3</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.7784423828125</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.7781297136450278</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.2215576171874994</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.7784423828125</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.2215576171875</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C86" t="b">
+        <v>0</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>R2C1</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.76708984375</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.7661749727091294</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.2329101562499994</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.76708984375</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.23291015625</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C87" t="b">
+        <v>0</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.7247314453125</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.7241922786895966</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.2752685546874994</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.7247314453125</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.2752685546875</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C88" t="b">
+        <v>0</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.7840576171875</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.7837361279091537</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.2159423828124994</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.7840576171875</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.2159423828125</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C89" t="b">
+        <v>0</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>R3C1</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.78076171875</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.780161933401568</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.2192382812499993</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.78076171875</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.21923828125</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C90" t="b">
+        <v>0</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.7279052734375</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.7278513813934757</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.2720947265624993</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.7279052734375</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.2720947265625</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C91" t="b">
+        <v>0</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>R3C3</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.7867431640625</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.7864581326942608</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.2132568359374993</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.7867431640625</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.2132568359375</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C92" t="b">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>R1C1</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.9473049872610493</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.944188316557822</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.06968282301249494</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.9473049872610493</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.05269501273895068</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.109375, "0001": 0.107177734375, "0010": 0.0108642578125, "0011": 0.011474609375, "0100": 0.108642578125, "0101": 0.1207275390625, "0110": 0.011962890625, "0111": 0.0115966796875, "1000": 0.0108642578125, "1001": 0.01123046875, "1010": 0.1195068359375, "1011": 0.1180419921875, "1100": 0.00927734375, "1101": 0.0108642578125, "1110": 0.1142578125, "1111": 0.1141357421875}, "3": {"0000": 0.1175537109375, "0001": 0.104736328125, "0010": 0.015869140625, "0011": 0.0164794921875, "0100": 0.1197509765625, "0101": 0.1080322265625, "0110": 0.014404296875, "0111": 0.0189208984375, "1000": 0.016357421875, "1001": 0.018310546875, "1010": 0.10595703125, "1011": 0.105224609375, "1100": 0.0203857421875, "1101": 0.01708984375, "1110": 0.1043701171875, "1111": 0.0965576171875}, "5": {"0000": 0.115234375, "0001": 0.10986328125, "0010": 0.021728515625, "0011": 0.017822265625, "0100": 0.108154296875, "0101": 0.1043701171875, "0110": 0.021484375, "0111": 0.0201416015625, "1000": 0.0164794921875, "1001": 0.0206298828125, "1010": 0.1014404296875, "1011": 0.1025390625, "1100": 0.0211181640625, "1101": 0.0194091796875, "1110": 0.105224609375, "1111": 0.0943603515625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C93" t="b">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>R1C2</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.846038818359375</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.8455358186127022</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.1539611816406249</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.846038818359375</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1539611816406251</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.0953369140625, "0001": 0.03173828125, "0010": 0.0999755859375, "0011": 0.031494140625, "0100": 0.100830078125, "0101": 0.0291748046875, "0110": 0.0946044921875, "0111": 0.0269775390625, "1000": 0.0245361328125, "1001": 0.09814453125, "1010": 0.0263671875, "1011": 0.092529296875, "1100": 0.028076171875, "1101": 0.0921630859375, "1110": 0.0296630859375, "1111": 0.098388671875}, "3": {"0000": 0.084716796875, "0001": 0.040283203125, "0010": 0.084716796875, "0011": 0.040283203125, "0100": 0.090576171875, "0101": 0.0419921875, "0110": 0.0833740234375, "0111": 0.044189453125, "1000": 0.0421142578125, "1001": 0.0826416015625, "1010": 0.04052734375, "1011": 0.0770263671875, "1100": 0.0482177734375, "1101": 0.0816650390625, "1110": 0.03955078125, "1111": 0.078125}, "5": {"0000": 0.075439453125, "0001": 0.052490234375, "0010": 0.0771484375, "0011": 0.048828125, "0100": 0.0748291015625, "0101": 0.0537109375, "0110": 0.078369140625, "0111": 0.046630859375, "1000": 0.0498046875, "1001": 0.077880859375, "1010": 0.0430908203125, "1011": 0.067138671875, "1100": 0.048583984375, "1101": 0.078125, "1110": 0.0511474609375, "1111": 0.0767822265625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C94" t="b">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>R1C3</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.895050048828125</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.8929982834574982</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.1098327636718749</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.895050048828125</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1049499511718751</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.029296875, "0001": 0.0919189453125, "0010": 0.0989990234375, "0011": 0.0235595703125, "0100": 0.0242919921875, "0101": 0.098876953125, "0110": 0.10498046875, "0111": 0.023681640625, "1000": 0.0999755859375, "1001": 0.0252685546875, "1010": 0.0216064453125, "1011": 0.1041259765625, "1100": 0.0958251953125, "1101": 0.0240478515625, "1110": 0.02685546875, "1111": 0.106689453125}, "3": {"0000": 0.047119140625, "0001": 0.083984375, "0010": 0.0911865234375, "0011": 0.0389404296875, "0100": 0.04296875, "0101": 0.0860595703125, "0110": 0.0833740234375, "0111": 0.0426025390625, "1000": 0.0867919921875, "1001": 0.0386962890625, "1010": 0.0355224609375, "1011": 0.0780029296875, "1100": 0.0830078125, "1101": 0.04345703125, "1110": 0.039306640625, "1111": 0.0789794921875}, "5": {"0000": 0.053466796875, "0001": 0.08349609375, "0010": 0.0819091796875, "0011": 0.0482177734375, "0100": 0.0472412109375, "0101": 0.0750732421875, "0110": 0.0797119140625, "0111": 0.04638671875, "1000": 0.0821533203125, "1001": 0.04541015625, "1010": 0.046630859375, "1011": 0.0665283203125, "1100": 0.07275390625, "1101": 0.0472412109375, "1110": 0.047607421875, "1111": 0.076171875}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C95" t="b">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>R2C1</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.9365539550781248</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.9354557601222871</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.0688934326171876</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.9365539550781248</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.06344604492187525</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.1075439453125, "0001": 0.10205078125, "0010": 0.023193359375, "0011": 0.020263671875, "0100": 0.0225830078125, "0101": 0.026123046875, "0110": 0.1048583984375, "0111": 0.1058349609375, "1000": 0.105712890625, "1001": 0.100830078125, "1010": 0.0247802734375, "1011": 0.0223388671875, "1100": 0.023193359375, "1101": 0.0211181640625, "1110": 0.0924072265625, "1111": 0.09716796875}, "3": {"0000": 0.0904541015625, "0001": 0.0858154296875, "0010": 0.0389404296875, "0011": 0.0462646484375, "0100": 0.042236328125, "0101": 0.0438232421875, "0110": 0.08349609375, "0111": 0.0762939453125, "1000": 0.0859375, "1001": 0.077392578125, "1010": 0.04345703125, "1011": 0.04345703125, "1100": 0.0435791015625, "1101": 0.0428466796875, "1110": 0.079345703125, "1111": 0.07666015625}, "5": {"0000": 0.07470703125, "0001": 0.07763671875, "0010": 0.0489501953125, "0011": 0.0533447265625, "0100": 0.052978515625, "0101": 0.054443359375, "0110": 0.077392578125, "0111": 0.072998046875, "1000": 0.080078125, "1001": 0.072998046875, "1010": 0.045166015625, "1011": 0.0478515625, "1100": 0.05078125, "1101": 0.04638671875, "1110": 0.0716552734375, "1111": 0.0726318359375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C96" t="b">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.8636322021484375</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.8628402409057812</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.1363677978515624</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.8636322021484375</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.1363677978515626</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.102783203125, "0001": 0.0252685546875, "0010": 0.0972900390625, "0011": 0.0328369140625, "0100": 0.0242919921875, "0101": 0.1002197265625, "0110": 0.0294189453125, "0111": 0.0986328125, "1000": 0.102294921875, "1001": 0.029541015625, "1010": 0.0946044921875, "1011": 0.0240478515625, "1100": 0.0244140625, "1101": 0.0970458984375, "1110": 0.0240478515625, "1111": 0.09326171875}, "3": {"0000": 0.0924072265625, "0001": 0.04052734375, "0010": 0.090576171875, "0011": 0.0438232421875, "0100": 0.042724609375, "0101": 0.080322265625, "0110": 0.0433349609375, "0111": 0.080322265625, "1000": 0.0845947265625, "1001": 0.0413818359375, "1010": 0.0845947265625, "1011": 0.0367431640625, "1100": 0.04150390625, "1101": 0.0784912109375, "1110": 0.0413818359375, "1111": 0.0772705078125}, "5": {"0000": 0.078369140625, "0001": 0.054931640625, "0010": 0.076416015625, "0011": 0.0496826171875, "0100": 0.0531005859375, "0101": 0.0762939453125, "0110": 0.051513671875, "0111": 0.078857421875, "1000": 0.0751953125, "1001": 0.049560546875, "1010": 0.0743408203125, "1011": 0.047607421875, "1100": 0.048095703125, "1101": 0.071533203125, "1110": 0.0445556640625, "1111": 0.0699462890625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C97" t="b">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.881591796875</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.8811498554594307</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.1184082031249999</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.881591796875</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.1184082031250002</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.026123046875, "0001": 0.1004638671875, "0010": 0.10205078125, "0011": 0.025390625, "0100": 0.099853515625, "0101": 0.0263671875, "0110": 0.0286865234375, "0111": 0.1004638671875, "1000": 0.027587890625, "1001": 0.0970458984375, "1010": 0.101318359375, "1011": 0.0250244140625, "1100": 0.0946044921875, "1101": 0.0240478515625, "1110": 0.025390625, "1111": 0.0955810546875}, "3": {"0000": 0.04248046875, "0001": 0.0848388671875, "0010": 0.0870361328125, "0011": 0.044921875, "0100": 0.086669921875, "0101": 0.0426025390625, "0110": 0.0435791015625, "0111": 0.0789794921875, "1000": 0.0406494140625, "1001": 0.0850830078125, "1010": 0.080810546875, "1011": 0.0418701171875, "1100": 0.0814208984375, "1101": 0.041015625, "1110": 0.043212890625, "1111": 0.0748291015625}, "5": {"0000": 0.0574951171875, "0001": 0.073974609375, "0010": 0.077880859375, "0011": 0.052734375, "0100": 0.075439453125, "0101": 0.045654296875, "0110": 0.05419921875, "0111": 0.07470703125, "1000": 0.0504150390625, "1001": 0.0732421875, "1010": 0.071533203125, "1011": 0.0511474609375, "1100": 0.0751953125, "1101": 0.0455322265625, "1110": 0.0499267578125, "1111": 0.0709228515625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C98" t="b">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>R3C1</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F98" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.8901519775390625</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.8897981784379481</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.1098480224609374</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.8901519775390625</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1098480224609376</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.1019287109375, "0001": 0.103759765625, "0010": 0.0233154296875, "0011": 0.02294921875, "0100": 0.02587890625, "0101": 0.025390625, "0110": 0.097900390625, "0111": 0.0982666015625, "1000": 0.0263671875, "1001": 0.02392578125, "1010": 0.103271484375, "1011": 0.1009521484375, "1100": 0.0977783203125, "1101": 0.09912109375, "1110": 0.0233154296875, "1111": 0.02587890625}, "3": {"0000": 0.092041015625, "0001": 0.0880126953125, "0010": 0.0369873046875, "0011": 0.0391845703125, "0100": 0.041748046875, "0101": 0.0404052734375, "0110": 0.0859375, "0111": 0.0775146484375, "1000": 0.04248046875, "1001": 0.0380859375, "1010": 0.0865478515625, "1011": 0.083740234375, "1100": 0.085693359375, "1101": 0.081787109375, "1110": 0.039306640625, "1111": 0.04052734375}, "5": {"0000": 0.0828857421875, "0001": 0.0784912109375, "0010": 0.0499267578125, "0011": 0.0484619140625, "0100": 0.0465087890625, "0101": 0.04931640625, "0110": 0.078369140625, "0111": 0.0758056640625, "1000": 0.04541015625, "1001": 0.0445556640625, "1010": 0.072998046875, "1011": 0.0804443359375, "1100": 0.0755615234375, "1101": 0.085205078125, "1110": 0.041015625, "1111": 0.0450439453125}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C99" t="b">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F99" t="n">
+        <v>3</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.8588104248046873</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.8568170376597776</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.1411895751953125</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.8588104248046873</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1411895751953128</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.0885009765625, "0001": 0.029296875, "0010": 0.0931396484375, "0011": 0.0355224609375, "0100": 0.0294189453125, "0101": 0.1016845703125, "0110": 0.0308837890625, "0111": 0.094482421875, "1000": 0.0279541015625, "1001": 0.0958251953125, "1010": 0.0291748046875, "1011": 0.0941162109375, "1100": 0.0982666015625, "1101": 0.02880859375, "1110": 0.0965576171875, "1111": 0.0263671875}, "3": {"0000": 0.085693359375, "0001": 0.04931640625, "0010": 0.083984375, "0011": 0.04443359375, "0100": 0.0494384765625, "0101": 0.0814208984375, "0110": 0.047119140625, "0111": 0.080078125, "1000": 0.0462646484375, "1001": 0.0745849609375, "1010": 0.04345703125, "1011": 0.070556640625, "1100": 0.0728759765625, "1101": 0.0418701171875, "1110": 0.081787109375, "1111": 0.047119140625}, "5": {"0000": 0.080322265625, "0001": 0.0587158203125, "0010": 0.0743408203125, "0011": 0.0517578125, "0100": 0.054443359375, "0101": 0.0765380859375, "0110": 0.0533447265625, "0111": 0.0675048828125, "1000": 0.0516357421875, "1001": 0.06640625, "1010": 0.0469970703125, "1011": 0.069580078125, "1100": 0.0758056640625, "1101": 0.053466796875, "1110": 0.070068359375, "1111": 0.049072265625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C100" t="b">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>R3C3</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>3</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.8815765380859375</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.8802591614822693</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.1199798583984374</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.8815765380859375</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1184234619140626</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.02880859375, "0001": 0.0970458984375, "0010": 0.0966796875, "0011": 0.0284423828125, "0100": 0.1114501953125, "0101": 0.0260009765625, "0110": 0.028564453125, "0111": 0.099609375, "1000": 0.09619140625, "1001": 0.0252685546875, "1010": 0.0262451171875, "1011": 0.0921630859375, "1100": 0.0230712890625, "1101": 0.0975341796875, "1110": 0.09912109375, "1111": 0.0238037109375}, "3": {"0000": 0.046630859375, "0001": 0.0848388671875, "0010": 0.087158203125, "0011": 0.0430908203125, "0100": 0.089111328125, "0101": 0.0462646484375, "0110": 0.0419921875, "0111": 0.083984375, "1000": 0.080322265625, "1001": 0.0428466796875, "1010": 0.0423583984375, "1011": 0.0816650390625, "1100": 0.0404052734375, "1101": 0.07470703125, "1110": 0.0809326171875, "1111": 0.03369140625}, "5": {"0000": 0.0528564453125, "0001": 0.0831298828125, "0010": 0.0712890625, "0011": 0.04931640625, "0100": 0.0772705078125, "0101": 0.052978515625, "0110": 0.04833984375, "0111": 0.073486328125, "1000": 0.078125, "1001": 0.044921875, "1010": 0.0478515625, "1011": 0.0765380859375, "1100": 0.048583984375, "1101": 0.076416015625, "1110": 0.07470703125, "1111": 0.044189453125}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C101" t="b">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>R1C1</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.9458312988281249</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.9456528117812298</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.05416870117187442</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.9458312988281249</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.05416870117187504</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.11376953125, "0001": 0.1165771484375, "0010": 0.011474609375, "0011": 0.0125732421875, "0100": 0.1190185546875, "0101": 0.1131591796875, "0110": 0.0146484375, "0111": 0.01220703125, "1000": 0.010498046875, "1001": 0.011474609375, "1010": 0.111572265625, "1011": 0.1112060546875, "1100": 0.0115966796875, "1101": 0.009521484375, "1110": 0.1082763671875, "1111": 0.1124267578125}, "3": {"0000": 0.109130859375, "0001": 0.10693359375, "0010": 0.0206298828125, "0011": 0.018798828125, "0100": 0.1138916015625, "0101": 0.1075439453125, "0110": 0.0162353515625, "0111": 0.0177001953125, "1000": 0.020263671875, "1001": 0.021484375, "1010": 0.1033935546875, "1011": 0.1068115234375, "1100": 0.02001953125, "1101": 0.0185546875, "1110": 0.09716796875, "1111": 0.1014404296875}, "5": {"0000": 0.1082763671875, "0001": 0.1025390625, "0010": 0.0234375, "0011": 0.0206298828125, "0100": 0.1060791015625, "0101": 0.103759765625, "0110": 0.0245361328125, "0111": 0.0240478515625, "1000": 0.023681640625, "1001": 0.0233154296875, "1010": 0.1025390625, "1011": 0.0972900390625, "1100": 0.021240234375, "1101": 0.02587890625, "1110": 0.0968017578125, "1111": 0.095947265625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C102" t="b">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>R1C2</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.8497619628906249</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.8490247295779186</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.1502380371093744</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.8497619628906249</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.1502380371093751</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.0960693359375, "0001": 0.0308837890625, "0010": 0.0936279296875, "0011": 0.03125, "0100": 0.09521484375, "0101": 0.0321044921875, "0110": 0.0936279296875, "0111": 0.0281982421875, "1000": 0.030517578125, "1001": 0.0975341796875, "1010": 0.031494140625, "1011": 0.09375, "1100": 0.028076171875, "1101": 0.0936279296875, "1110": 0.029052734375, "1111": 0.094970703125}, "3": {"0000": 0.0772705078125, "0001": 0.0458984375, "0010": 0.0848388671875, "0011": 0.04638671875, "0100": 0.0828857421875, "0101": 0.0491943359375, "0110": 0.07763671875, "0111": 0.05224609375, "1000": 0.0487060546875, "1001": 0.0750732421875, "1010": 0.044921875, "1011": 0.07958984375, "1100": 0.04296875, "1101": 0.0762939453125, "1110": 0.0428466796875, "1111": 0.0732421875}, "5": {"0000": 0.0706787109375, "0001": 0.0528564453125, "0010": 0.068603515625, "0011": 0.0518798828125, "0100": 0.0780029296875, "0101": 0.060791015625, "0110": 0.0677490234375, "0111": 0.0540771484375, "1000": 0.0570068359375, "1001": 0.073486328125, "1010": 0.0518798828125, "1011": 0.0677490234375, "1100": 0.0521240234375, "1101": 0.06787109375, "1110": 0.0560302734375, "1111": 0.0692138671875}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C103" t="b">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>R1C3</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.8824462890624999</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.881503726465764</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.1175537109374996</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.8824462890624999</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.1175537109375002</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.0283203125, "0001": 0.09375, "0010": 0.096923828125, "0011": 0.0286865234375, "0100": 0.027587890625, "0101": 0.0997314453125, "0110": 0.1029052734375, "0111": 0.0279541015625, "1000": 0.10205078125, "1001": 0.0263671875, "1010": 0.02978515625, "1011": 0.09033203125, "1100": 0.094482421875, "1101": 0.0250244140625, "1110": 0.028076171875, "1111": 0.0980224609375}, "3": {"0000": 0.0484619140625, "0001": 0.0810546875, "0010": 0.081298828125, "0011": 0.0423583984375, "0100": 0.0499267578125, "0101": 0.07958984375, "0110": 0.082275390625, "0111": 0.04443359375, "1000": 0.0765380859375, "1001": 0.0469970703125, "1010": 0.046875, "1011": 0.07275390625, "1100": 0.0810546875, "1101": 0.0433349609375, "1110": 0.044189453125, "1111": 0.078857421875}, "5": {"0000": 0.0550537109375, "0001": 0.072509765625, "0010": 0.07080078125, "0011": 0.0537109375, "0100": 0.0595703125, "0101": 0.0758056640625, "0110": 0.0753173828125, "0111": 0.049560546875, "1000": 0.0689697265625, "1001": 0.050048828125, "1010": 0.0521240234375, "1011": 0.0721435546875, "1100": 0.0677490234375, "1101": 0.0543212890625, "1110": 0.052001953125, "1111": 0.0703125}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>R2C1</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.7941436767578125</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.7935615854917729</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.2058563232421869</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.7941436767578125</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.2058563232421876</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.09326171875, "0001": 0.09033203125, "0010": 0.0330810546875, "0011": 0.0362548828125, "0100": 0.0362548828125, "0101": 0.035888671875, "0110": 0.087646484375, "0111": 0.093505859375, "1000": 0.0889892578125, "1001": 0.091064453125, "1010": 0.0328369140625, "1011": 0.034423828125, "1100": 0.03173828125, "1101": 0.030029296875, "1110": 0.0899658203125, "1111": 0.0947265625}, "3": {"0000": 0.07958984375, "0001": 0.0728759765625, "0010": 0.0489501953125, "0011": 0.048583984375, "0100": 0.050048828125, "0101": 0.0460205078125, "0110": 0.0830078125, "0111": 0.079345703125, "1000": 0.0782470703125, "1001": 0.0762939453125, "1010": 0.0487060546875, "1011": 0.0457763671875, "1100": 0.045166015625, "1101": 0.04541015625, "1110": 0.0731201171875, "1111": 0.078857421875}, "5": {"0000": 0.0672607421875, "0001": 0.0677490234375, "0010": 0.0531005859375, "0011": 0.05712890625, "0100": 0.0621337890625, "0101": 0.0557861328125, "0110": 0.068115234375, "0111": 0.0704345703125, "1000": 0.07666015625, "1001": 0.0667724609375, "1010": 0.052978515625, "1011": 0.05615234375, "1100": 0.061279296875, "1101": 0.06005859375, "1110": 0.0625, "1111": 0.0618896484375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C105" t="b">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>R2C2</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.8049011230468749</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.8038640525385988</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.1950988769531245</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.8049011230468749</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.1950988769531252</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.09326171875, "0001": 0.038330078125, "0010": 0.086181640625, "0011": 0.0367431640625, "0100": 0.03955078125, "0101": 0.0892333984375, "0110": 0.0341796875, "0111": 0.091796875, "1000": 0.0863037109375, "1001": 0.03369140625, "1010": 0.0943603515625, "1011": 0.033203125, "1100": 0.0369873046875, "1101": 0.093017578125, "1110": 0.0323486328125, "1111": 0.080810546875}, "3": {"0000": 0.07666015625, "0001": 0.0526123046875, "0010": 0.070068359375, "0011": 0.0474853515625, "0100": 0.056640625, "0101": 0.077880859375, "0110": 0.0516357421875, "0111": 0.072998046875, "1000": 0.0745849609375, "1001": 0.049560546875, "1010": 0.0797119140625, "1011": 0.0499267578125, "1100": 0.05224609375, "1101": 0.0694580078125, "1110": 0.0511474609375, "1111": 0.0673828125}, "5": {"0000": 0.0701904296875, "0001": 0.05859375, "0010": 0.067626953125, "0011": 0.0589599609375, "0100": 0.0621337890625, "0101": 0.0648193359375, "0110": 0.061767578125, "0111": 0.0726318359375, "1000": 0.0655517578125, "1001": 0.05322265625, "1010": 0.068115234375, "1011": 0.0574951171875, "1100": 0.0555419921875, "1101": 0.064453125, "1110": 0.0582275390625, "1111": 0.0606689453125}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C106" t="b">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.8567810058593749</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.8555822089958137</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.1432189941406245</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.8567810058593749</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.1432189941406251</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.0311279296875, "0001": 0.095947265625, "0010": 0.0933837890625, "0011": 0.0303955078125, "0100": 0.0943603515625, "0101": 0.0335693359375, "0110": 0.02978515625, "0111": 0.1031494140625, "1000": 0.030517578125, "1001": 0.0894775390625, "1010": 0.0904541015625, "1011": 0.030029296875, "1100": 0.095703125, "1101": 0.028076171875, "1110": 0.028076171875, "1111": 0.095947265625}, "3": {"0000": 0.0494384765625, "0001": 0.0777587890625, "0010": 0.0780029296875, "0011": 0.0474853515625, "0100": 0.08154296875, "0101": 0.044677734375, "0110": 0.0499267578125, "0111": 0.0777587890625, "1000": 0.0511474609375, "1001": 0.0787353515625, "1010": 0.077880859375, "1011": 0.047607421875, "1100": 0.07373046875, "1101": 0.0433349609375, "1110": 0.0458984375, "1111": 0.0750732421875}, "5": {"0000": 0.052490234375, "0001": 0.0706787109375, "0010": 0.07080078125, "0011": 0.05859375, "0100": 0.0731201171875, "0101": 0.0574951171875, "0110": 0.056640625, "0111": 0.069580078125, "1000": 0.054443359375, "1001": 0.0711669921875, "1010": 0.0704345703125, "1011": 0.051513671875, "1100": 0.0726318359375, "1101": 0.054931640625, "1110": 0.052978515625, "1111": 0.0625}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C107" t="b">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>R3C1</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.9138793945312498</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.9113547287386941</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.1008911132812496</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.9138793945312498</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.08612060546875015</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.10205078125, "0001": 0.1005859375, "0010": 0.0263671875, "0011": 0.024658203125, "0100": 0.0233154296875, "0101": 0.0263671875, "0110": 0.09619140625, "0111": 0.0992431640625, "1000": 0.0230712890625, "1001": 0.02587890625, "1010": 0.0986328125, "1011": 0.10009765625, "1100": 0.095947265625, "1101": 0.1082763671875, "1110": 0.02392578125, "1111": 0.025390625}, "3": {"0000": 0.0902099609375, "0001": 0.072998046875, "0010": 0.047119140625, "0011": 0.0482177734375, "0100": 0.04638671875, "0101": 0.0487060546875, "0110": 0.078369140625, "0111": 0.07568359375, "1000": 0.047119140625, "1001": 0.04443359375, "1010": 0.0833740234375, "1011": 0.0775146484375, "1100": 0.085205078125, "1101": 0.0712890625, "1110": 0.042724609375, "1111": 0.0406494140625}, "5": {"0000": 0.077880859375, "0001": 0.0709228515625, "0010": 0.0574951171875, "0011": 0.0543212890625, "0100": 0.0577392578125, "0101": 0.0577392578125, "0110": 0.0693359375, "0111": 0.06689453125, "1000": 0.0562744140625, "1001": 0.060791015625, "1010": 0.0634765625, "1011": 0.06494140625, "1100": 0.06494140625, "1101": 0.0689697265625, "1110": 0.0538330078125, "1111": 0.054443359375}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C108" t="b">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>R3C2</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.7608032226562498</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.7583798914572639</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.2391967773437495</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.7608032226562498</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.2391967773437502</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.094482421875, "0001": 0.0380859375, "0010": 0.082275390625, "0011": 0.0362548828125, "0100": 0.0341796875, "0101": 0.0908203125, "0110": 0.0400390625, "0111": 0.0823974609375, "1000": 0.0390625, "1001": 0.0863037109375, "1010": 0.044189453125, "1011": 0.086669921875, "1100": 0.084716796875, "1101": 0.039794921875, "1110": 0.0780029296875, "1111": 0.042724609375}, "3": {"0000": 0.0772705078125, "0001": 0.056396484375, "0010": 0.0743408203125, "0011": 0.0517578125, "0100": 0.055419921875, "0101": 0.0709228515625, "0110": 0.051025390625, "0111": 0.075439453125, "1000": 0.05078125, "1001": 0.0653076171875, "1010": 0.054931640625, "1011": 0.0654296875, "1100": 0.0777587890625, "1101": 0.0478515625, "1110": 0.0728759765625, "1111": 0.052490234375}, "5": {"0000": 0.07275390625, "0001": 0.0577392578125, "0010": 0.06689453125, "0011": 0.0587158203125, "0100": 0.066650390625, "0101": 0.0645751953125, "0110": 0.0614013671875, "0111": 0.0677490234375, "1000": 0.058837890625, "1001": 0.060302734375, "1010": 0.05224609375, "1011": 0.06640625, "1100": 0.0670166015625, "1101": 0.0543212890625, "1110": 0.06591796875, "1111": 0.0584716796875}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>R3C3</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>8192</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.8588714599609374</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.8576015949124506</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.1411285400390619</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.8588714599609374</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.1411285400390626</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>{"1": {"0000": 0.0274658203125, "0001": 0.1031494140625, "0010": 0.0977783203125, "0011": 0.0260009765625, "0100": 0.10009765625, "0101": 0.029296875, "0110": 0.029052734375, "0111": 0.09765625, "1000": 0.0906982421875, "1001": 0.02734375, "1010": 0.027587890625, "1011": 0.1002197265625, "1100": 0.02685546875, "1101": 0.0946044921875, "1110": 0.0970458984375, "1111": 0.025146484375}, "3": {"0000": 0.04638671875, "0001": 0.08740234375, "0010": 0.0810546875, "0011": 0.039794921875, "0100": 0.0906982421875, "0101": 0.0419921875, "0110": 0.041259765625, "0111": 0.0809326171875, "1000": 0.08837890625, "1001": 0.0445556640625, "1010": 0.0391845703125, "1011": 0.0791015625, "1100": 0.0430908203125, "1101": 0.0782470703125, "1110": 0.0809326171875, "1111": 0.0369873046875}, "5": {"0000": 0.052001953125, "0001": 0.079833984375, "0010": 0.0794677734375, "0011": 0.047607421875, "0100": 0.0789794921875, "0101": 0.053466796875, "0110": 0.0478515625, "0111": 0.0791015625, "1000": 0.076904296875, "1001": 0.0498046875, "1010": 0.0487060546875, "1011": 0.0693359375, "1100": 0.0478515625, "1101": 0.071044921875, "1110": 0.0718994140625, "1111": 0.046142578125}}</t>
         </is>
       </c>
     </row>
@@ -2729,7 +6937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2779,87 +6987,89 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noise_levels</t>
+          <t>preservation_levels</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>["hardware"]</t>
+          <t>["low", "medium", "high"]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>circuit_types</t>
+          <t>local_simulation_noise</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>["contextuality-preserving", "baseline"]</t>
+          <t>{"single_qubit_depol": 0.003, "two_qubit_depol": 0.02, "readout_p01": 0.02, "readout_p10": 0.02}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mitigation_modes</t>
+          <t>circuit_types</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[false, true]</t>
+          <t>["contextuality-preserving", "baseline"]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>contexts</t>
+          <t>mitigation_modes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>["R1C1", "R1C2", "R1C3", "R2C1", "R2C2", "R2C3", "R3C1", "R3C2", "R3C3"]</t>
+          <t>[false, true]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>backend_name</t>
+          <t>contexts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>["R1C1", "R1C2", "R1C3", "R2C1", "R2C2", "R2C3", "R3C1", "R3C2", "R3C3"]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>use_real_backend</t>
-        </is>
-      </c>
-      <c r="B10" t="b">
-        <v>1</v>
+          <t>backend_name</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>use_backend_mimic</t>
+          <t>use_real_backend</t>
         </is>
       </c>
       <c r="B11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>smoke_test</t>
+          <t>use_backend_mimic</t>
         </is>
       </c>
       <c r="B12" t="b">
@@ -2869,11 +7079,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>smoke_test</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>generated_at_unix</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1776032839.349274</v>
+      <c r="B14" t="n">
+        <v>1776042457.595276</v>
       </c>
     </row>
   </sheetData>
@@ -2887,13 +7107,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>noise_level</t>
+          <t>preservation_level</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2930,7 +7150,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2942,22 +7162,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.792277</v>
+        <v>0.780002</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.79193</v>
+        <v>0.779635</v>
       </c>
       <c r="G2" t="n">
-        <v>0.207723</v>
+        <v>0.219998</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2969,22 +7189,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.81212</v>
+        <v>0.803779</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.811817</v>
+        <v>0.8035060000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.18788</v>
+        <v>0.196221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2996,22 +7216,22 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.881124</v>
+        <v>0.851935</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.87993</v>
+        <v>0.850725</v>
       </c>
       <c r="G4" t="n">
-        <v>0.120287</v>
+        <v>0.149706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3023,16 +7243,232 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.893216</v>
+        <v>0.888968</v>
       </c>
       <c r="E5" t="n">
-        <v>0.038943</v>
+        <v>0.000711</v>
       </c>
       <c r="F5" t="n">
-        <v>0.891888</v>
+        <v>0.887671</v>
       </c>
       <c r="G5" t="n">
-        <v>0.111118</v>
+        <v>0.11424</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7536620000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.753286</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.246338</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.782267</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.781801</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.217733</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.876795</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.875097</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.125205</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.87946</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.877934</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.123355</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.756266</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.755848</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.243734</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.807644</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.807351</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.192356</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.875714</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.874489</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.128103</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.890359</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.013229</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.889409</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.111196</v>
       </c>
     </row>
   </sheetData>
@@ -3046,7 +7482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3096,27 +7532,65 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noise_level</t>
+          <t>preservation_level</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.87993</v>
+        <v>0.875097</v>
       </c>
       <c r="C4" t="n">
-        <v>0.79193</v>
+        <v>0.753286</v>
       </c>
       <c r="D4" t="n">
-        <v>0.891888</v>
+        <v>0.877934</v>
       </c>
       <c r="E4" t="n">
-        <v>0.811817</v>
+        <v>0.781801</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.874489</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.755848</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.889409</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.807351</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.850725</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.779635</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.887671</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8035060000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3134,7 +7608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3184,27 +7658,65 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noise_level</t>
+          <t>preservation_level</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.881124</v>
+        <v>0.876795</v>
       </c>
       <c r="C4" t="n">
-        <v>0.792277</v>
+        <v>0.7536620000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.893216</v>
+        <v>0.87946</v>
       </c>
       <c r="E4" t="n">
-        <v>0.81212</v>
+        <v>0.782267</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.875714</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.756266</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.890359</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.807644</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.851935</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.780002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.888968</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.803779</v>
       </c>
     </row>
   </sheetData>
@@ -3222,7 +7734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3272,14 +7784,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noise_level</t>
+          <t>preservation_level</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3289,9 +7801,47 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.038943</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.013229</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.000711</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3310,13 +7860,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>noise_level</t>
+          <t>preservation_level</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3348,45 +7898,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B2" t="b">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.019843</v>
+        <v>0.023777</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.019886</v>
+        <v>0.023871</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.019843</v>
+        <v>-0.023777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>high</t>
         </is>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.012092</v>
+        <v>0.037032</v>
       </c>
       <c r="D3" t="n">
-        <v>0.038943</v>
+        <v>0.000711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.011957</v>
+        <v>0.036946</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.009168000000000001</v>
+        <v>-0.035465</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.028605</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.028515</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.028605</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.002664</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.002837</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.00185</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.051378</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.051503</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.051378</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.014645</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.013229</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.016907</v>
       </c>
     </row>
   </sheetData>
@@ -3400,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3411,7 +8049,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>noise_level</t>
+          <t>preservation_level</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -3443,44 +8081,140 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.088847</v>
+        <v>0.123133</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.12181</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.087436</v>
+        <v>-0.121133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.119447</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.118642</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.115631</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.071933</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07109</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.07029199999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>contextuality-preserving</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>hardware</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.081096</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.038943</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.080071</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.076761</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.097192</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.096133</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.094378</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.082715</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.013229</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.08205800000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.08116</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>contextuality-preserving</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.085189</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000711</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.084166</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.081981</v>
       </c>
     </row>
   </sheetData>
